--- a/input_home.xlsx
+++ b/input_home.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO10"/>
+  <dimension ref="A1:BN10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,43 +421,43 @@
         <v>24</v>
       </c>
       <c r="B1" t="n">
-        <v>14.86486721351971</v>
+        <v>2.624645600029241</v>
       </c>
       <c r="C1" t="n">
-        <v>0.9336343207222382</v>
+        <v>0.4228944371259503</v>
       </c>
       <c r="D1" t="n">
-        <v>0.002863745783304669</v>
+        <v>0.2810341347701197</v>
       </c>
       <c r="E1" t="n">
-        <v>3.247202298058066</v>
+        <v>4.116057044790626</v>
       </c>
       <c r="F1" t="n">
-        <v>0.6769653741861182</v>
+        <v>0.3142191666020036</v>
       </c>
       <c r="G1" t="n">
-        <v>42.27630672670247</v>
+        <v>18.60151215651894</v>
       </c>
       <c r="H1" t="n">
-        <v>3.588779763383489</v>
+        <v>6.253301110188477</v>
       </c>
       <c r="I1" t="n">
-        <v>4.886391066817031</v>
+        <v>5.364750203884915</v>
       </c>
       <c r="J1" t="n">
-        <v>5.516825164077503</v>
+        <v>4.899029623522595</v>
       </c>
       <c r="K1" t="n">
-        <v>2.113346937070531</v>
+        <v>2.014822160715529</v>
       </c>
       <c r="L1" t="n">
-        <v>5.030597429359485</v>
+        <v>7.810663544479673</v>
       </c>
       <c r="M1" t="n">
-        <v>1.467500571600376</v>
+        <v>6.93776815056832</v>
       </c>
       <c r="N1" t="n">
-        <v>5.86709002576029</v>
+        <v>4.431571414529405</v>
       </c>
       <c r="O1" t="n">
         <v>104.65</v>
@@ -472,7 +472,7 @@
         <v>0.35</v>
       </c>
       <c r="S1" t="n">
-        <v>1.524914114449834</v>
+        <v>1.263740054081372</v>
       </c>
       <c r="T1" t="n">
         <v>0</v>
@@ -481,141 +481,138 @@
         <v>0</v>
       </c>
       <c r="V1" t="n">
-        <v>2.733646402136745</v>
+        <v>7.124950399672182</v>
       </c>
       <c r="W1" t="n">
         <v>100000</v>
       </c>
       <c r="X1" t="n">
-        <v>4.960232915996539</v>
+        <v>1.75736785659399</v>
       </c>
       <c r="Y1" t="n">
-        <v>0.2985046546352792</v>
+        <v>46.01476016327929</v>
       </c>
       <c r="Z1" t="n">
-        <v>0.1432043512639642</v>
+        <v>0.01738875929471901</v>
       </c>
       <c r="AA1" t="n">
-        <v>0.2700890467620114</v>
+        <v>0.001702756636837158</v>
       </c>
       <c r="AB1" t="n">
+        <v>0.003569365467709305</v>
+      </c>
+      <c r="AC1" t="n">
         <v>0.7</v>
       </c>
-      <c r="AC1" t="n">
+      <c r="AD1" t="n">
+        <v>36.12360591992946</v>
+      </c>
+      <c r="AE1" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD1" t="n">
-        <v>0.143393898043621</v>
-      </c>
-      <c r="AE1" t="n">
-        <v>47.22672727923468</v>
-      </c>
       <c r="AF1" t="n">
-        <v>70.37851393134741</v>
+        <v>0.005109327303276984</v>
       </c>
       <c r="AG1" t="n">
-        <v>0.5</v>
+        <v>48</v>
       </c>
       <c r="AH1" t="n">
-        <v>0.11</v>
+        <v>30.46</v>
       </c>
       <c r="AI1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AJ1" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK1" t="n">
         <v>0.83</v>
       </c>
-      <c r="AJ1" t="n">
-        <v>3.245646382518976</v>
-      </c>
-      <c r="AK1" t="n">
-        <v>7.277586598248925</v>
-      </c>
       <c r="AL1" t="n">
-        <v>0</v>
+        <v>3.573000931818117</v>
       </c>
       <c r="AM1" t="n">
-        <v>2.137486532436598</v>
+        <v>1.687373891864628</v>
       </c>
       <c r="AN1" t="n">
-        <v>23.16998157788103</v>
+        <v>0</v>
       </c>
       <c r="AO1" t="n">
-        <v>1.5</v>
+        <v>7.318611302671671</v>
       </c>
       <c r="AP1" t="n">
-        <v>0.11</v>
+        <v>10.9702589057802</v>
       </c>
       <c r="AQ1" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AR1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS1" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AT1" t="n">
         <v>1.3</v>
       </c>
-      <c r="AR1" t="n">
-        <v>20.12661839428246</v>
-      </c>
-      <c r="AS1" t="n">
-        <v>1.03334506693412</v>
-      </c>
-      <c r="AT1" t="n">
-        <v>22.07492619901768</v>
-      </c>
       <c r="AU1" t="n">
-        <v>23.47586100270521</v>
+        <v>26.86961404004723</v>
       </c>
       <c r="AV1" t="n">
-        <v>16.9303283669795</v>
+        <v>33.21678618168145</v>
       </c>
       <c r="AW1" t="n">
-        <v>1.992384137057159</v>
+        <v>1.202319134755185</v>
       </c>
       <c r="AX1" t="n">
-        <v>125</v>
+        <v>65.16556038134323</v>
       </c>
       <c r="AY1" t="n">
-        <v>58</v>
+        <v>44.90952109089307</v>
       </c>
       <c r="AZ1" t="n">
-        <v>971</v>
+        <v>9.773739567201234</v>
       </c>
       <c r="BA1" t="n">
-        <v>1.037</v>
+        <v>-1.619</v>
       </c>
       <c r="BB1" t="n">
-        <v>756</v>
+        <v>8592</v>
       </c>
       <c r="BC1" t="n">
-        <v>0.516</v>
+        <v>0.0015</v>
       </c>
       <c r="BD1" t="n">
-        <v>0.165</v>
+        <v>1769.8</v>
       </c>
       <c r="BE1" t="n">
-        <v>1769.8</v>
+        <v>258.5</v>
       </c>
       <c r="BF1" t="n">
-        <v>258.5</v>
+        <v>0.234</v>
       </c>
       <c r="BG1" t="n">
-        <v>0.234</v>
+        <v>7.785</v>
       </c>
       <c r="BH1" t="n">
-        <v>7.785</v>
+        <v>0.15</v>
       </c>
       <c r="BI1" t="n">
-        <v>0.15</v>
+        <v>1.36</v>
       </c>
       <c r="BJ1" t="n">
-        <v>1.36</v>
+        <v>72.47799999999999</v>
       </c>
       <c r="BK1" t="n">
-        <v>72.47799999999999</v>
+        <v>0.131</v>
       </c>
       <c r="BL1" t="n">
-        <v>0.131</v>
+        <v>22.034</v>
       </c>
       <c r="BM1" t="n">
-        <v>22.034</v>
+        <v>3.284</v>
       </c>
       <c r="BN1" t="n">
-        <v>3.284</v>
-      </c>
-      <c r="BO1" t="n">
         <v>35.752</v>
       </c>
     </row>
@@ -624,43 +621,43 @@
         <v>24</v>
       </c>
       <c r="B2" t="n">
-        <v>73.2664522309028</v>
+        <v>44.85650495655575</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007406548483288461</v>
+        <v>0.6808462791064019</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3588793699996433</v>
+        <v>0.2511618504833931</v>
       </c>
       <c r="E2" t="n">
-        <v>9.396797552664831</v>
+        <v>19.40246901111095</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1019285297386612</v>
+        <v>0.01090105049175251</v>
       </c>
       <c r="G2" t="n">
-        <v>1.50891518167804</v>
+        <v>19.35563959336351</v>
       </c>
       <c r="H2" t="n">
-        <v>1.993820345254216</v>
+        <v>2.436768951909658</v>
       </c>
       <c r="I2" t="n">
-        <v>2.729923506468542</v>
+        <v>1.87184491915933</v>
       </c>
       <c r="J2" t="n">
-        <v>5.285696788353456</v>
+        <v>2.17427710084455</v>
       </c>
       <c r="K2" t="n">
-        <v>1.346899386375183</v>
+        <v>1.03773994997315</v>
       </c>
       <c r="L2" t="n">
-        <v>1.364877334373306</v>
+        <v>4.690950557246325</v>
       </c>
       <c r="M2" t="n">
-        <v>1.321321698950693</v>
+        <v>3.599072332263632</v>
       </c>
       <c r="N2" t="n">
-        <v>2.599675386657246</v>
+        <v>6.756196035316291</v>
       </c>
       <c r="O2" t="n">
         <v>104.65</v>
@@ -675,7 +672,7 @@
         <v>0.35</v>
       </c>
       <c r="S2" t="n">
-        <v>1.101075956870546</v>
+        <v>8.117629931541151</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -684,141 +681,138 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>3.543535970209363</v>
+        <v>24.72759810976516</v>
       </c>
       <c r="W2" t="n">
         <v>100000</v>
       </c>
       <c r="X2" t="n">
-        <v>21.2209154372387</v>
+        <v>27.67994256643322</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.7280906459209183</v>
+        <v>11.14537479901405</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2531630668203078</v>
+        <v>0.2660224919712854</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1029312486126932</v>
+        <v>0.05897129168709031</v>
       </c>
       <c r="AB2" t="n">
+        <v>0.003566727209156357</v>
+      </c>
+      <c r="AC2" t="n">
         <v>0.7</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
+        <v>67.0285855464958</v>
+      </c>
+      <c r="AE2" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD2" t="n">
-        <v>0.008073156798270359</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>47.56138026838401</v>
-      </c>
       <c r="AF2" t="n">
-        <v>56.42299867973075</v>
+        <v>0.02438167935364367</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.5</v>
+        <v>48</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.11</v>
+        <v>30.46</v>
       </c>
       <c r="AI2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK2" t="n">
         <v>0.83</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>1.029925089146845</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>8.765634717174986</v>
-      </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>2.130257969753776</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.19461678567519</v>
+        <v>1.176174929189934</v>
       </c>
       <c r="AN2" t="n">
-        <v>37.32619859399745</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>2.5</v>
+        <v>1.752394608421528</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.11</v>
+        <v>44.0481412728826</v>
       </c>
       <c r="AQ2" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AT2" t="n">
         <v>1.3</v>
       </c>
-      <c r="AR2" t="n">
-        <v>46.62483392029357</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.650513568311224</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>30.97739601118172</v>
-      </c>
       <c r="AU2" t="n">
-        <v>6.046920847580861</v>
+        <v>29.79411227241708</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.83602894660395</v>
+        <v>37.05913948851506</v>
       </c>
       <c r="AW2" t="n">
-        <v>27.00831548307504</v>
+        <v>35.94172287759414</v>
       </c>
       <c r="AX2" t="n">
-        <v>125</v>
+        <v>156.9674538360569</v>
       </c>
       <c r="AY2" t="n">
-        <v>58</v>
+        <v>304.2870852845749</v>
       </c>
       <c r="AZ2" t="n">
-        <v>971</v>
+        <v>16.24659006067941</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.037</v>
+        <v>-1.619</v>
       </c>
       <c r="BB2" t="n">
-        <v>756</v>
+        <v>8592</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.516</v>
+        <v>0.0015</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.165</v>
+        <v>1769.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>1769.8</v>
+        <v>258.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>258.5</v>
+        <v>0.234</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.234</v>
+        <v>7.785</v>
       </c>
       <c r="BH2" t="n">
-        <v>7.785</v>
+        <v>0.15</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.15</v>
+        <v>1.36</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.36</v>
+        <v>72.47799999999999</v>
       </c>
       <c r="BK2" t="n">
-        <v>72.47799999999999</v>
+        <v>0.131</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.131</v>
+        <v>22.034</v>
       </c>
       <c r="BM2" t="n">
-        <v>22.034</v>
+        <v>3.284</v>
       </c>
       <c r="BN2" t="n">
-        <v>3.284</v>
-      </c>
-      <c r="BO2" t="n">
         <v>35.752</v>
       </c>
     </row>
@@ -827,43 +821,43 @@
         <v>24</v>
       </c>
       <c r="B3" t="n">
-        <v>49.42509733655319</v>
+        <v>72.04584992142473</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0282135832799881</v>
+        <v>0.2381540859288045</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08507449727332718</v>
+        <v>0.01189945937319243</v>
       </c>
       <c r="E3" t="n">
-        <v>27.48599978954534</v>
+        <v>2.6840551610534</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1523907121541738</v>
+        <v>0.003233636010512297</v>
       </c>
       <c r="G3" t="n">
-        <v>2.997981245713293</v>
+        <v>13.90231441599097</v>
       </c>
       <c r="H3" t="n">
-        <v>6.243373155575673</v>
+        <v>1.139905863614229</v>
       </c>
       <c r="I3" t="n">
-        <v>1.362608683023906</v>
+        <v>3.758281156676661</v>
       </c>
       <c r="J3" t="n">
-        <v>1.843653870670102</v>
+        <v>1.838640293684266</v>
       </c>
       <c r="K3" t="n">
-        <v>2.026825982952242</v>
+        <v>3.19483913868564</v>
       </c>
       <c r="L3" t="n">
-        <v>2.892700212732175</v>
+        <v>4.084411087108841</v>
       </c>
       <c r="M3" t="n">
-        <v>1.405605159610745</v>
+        <v>3.73446011869645</v>
       </c>
       <c r="N3" t="n">
-        <v>4.65841304990888</v>
+        <v>4.390858836650517</v>
       </c>
       <c r="O3" t="n">
         <v>104.65</v>
@@ -878,7 +872,7 @@
         <v>0.35</v>
       </c>
       <c r="S3" t="n">
-        <v>8.93503761077327</v>
+        <v>6.038934534884967</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -887,141 +881,138 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>3.076436989131095</v>
+        <v>14.51033957738572</v>
       </c>
       <c r="W3" t="n">
         <v>100000</v>
       </c>
       <c r="X3" t="n">
-        <v>56.19598876813254</v>
+        <v>2.002041691731496</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5290166013632849</v>
+        <v>17.12669450873294</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3696105182137062</v>
+        <v>0.003093478113085225</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004457041920171548</v>
+        <v>0.2127344662474048</v>
       </c>
       <c r="AB3" t="n">
+        <v>0.005975387162449763</v>
+      </c>
+      <c r="AC3" t="n">
         <v>0.7</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
+        <v>18.88685916176554</v>
+      </c>
+      <c r="AE3" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD3" t="n">
-        <v>0.1898142125211391</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>47.06412312783145</v>
-      </c>
       <c r="AF3" t="n">
-        <v>27.27968652117235</v>
+        <v>0.02865772374866126</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.5</v>
+        <v>48</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.11</v>
+        <v>30.46</v>
       </c>
       <c r="AI3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK3" t="n">
         <v>0.83</v>
       </c>
-      <c r="AJ3" t="n">
-        <v>1.623598935333417</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>8.961207346070555</v>
-      </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.049830118963201</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.14835980629361</v>
+        <v>5.677049928370925</v>
       </c>
       <c r="AN3" t="n">
-        <v>23.72641395850215</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
+        <v>4.358090737163947</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>37.24801365598864</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AR3" t="n">
         <v>1</v>
       </c>
-      <c r="AP3" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AQ3" t="n">
+      <c r="AS3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AT3" t="n">
         <v>1.3</v>
       </c>
-      <c r="AR3" t="n">
-        <v>16.31200199025767</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0.8219090261868272</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.695404845873487</v>
-      </c>
       <c r="AU3" t="n">
-        <v>24.89852358332788</v>
+        <v>12.27658546818892</v>
       </c>
       <c r="AV3" t="n">
-        <v>168.9232666736632</v>
+        <v>5.146530404836336</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.337114357632195</v>
+        <v>10.4684860026725</v>
       </c>
       <c r="AX3" t="n">
-        <v>125</v>
+        <v>76.10126448943824</v>
       </c>
       <c r="AY3" t="n">
-        <v>58</v>
+        <v>10.67874889417739</v>
       </c>
       <c r="AZ3" t="n">
-        <v>971</v>
+        <v>5.929524390110897</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.037</v>
+        <v>-1.619</v>
       </c>
       <c r="BB3" t="n">
-        <v>756</v>
+        <v>8592</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.516</v>
+        <v>0.0015</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.165</v>
+        <v>1769.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1769.8</v>
+        <v>258.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>258.5</v>
+        <v>0.234</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.234</v>
+        <v>7.785</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.785</v>
+        <v>0.15</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.15</v>
+        <v>1.36</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.36</v>
+        <v>72.47799999999999</v>
       </c>
       <c r="BK3" t="n">
-        <v>72.47799999999999</v>
+        <v>0.131</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.131</v>
+        <v>22.034</v>
       </c>
       <c r="BM3" t="n">
-        <v>22.034</v>
+        <v>3.284</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.284</v>
-      </c>
-      <c r="BO3" t="n">
         <v>35.752</v>
       </c>
     </row>
@@ -1030,43 +1021,43 @@
         <v>24</v>
       </c>
       <c r="B4" t="n">
-        <v>16.51520890538957</v>
+        <v>5.663885870405019</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05752826012772017</v>
+        <v>0.009227019733043839</v>
       </c>
       <c r="D4" t="n">
-        <v>0.146143092658319</v>
+        <v>0.0925875865936997</v>
       </c>
       <c r="E4" t="n">
-        <v>24.87778906487593</v>
+        <v>7.57040955314132</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9081841602017848</v>
+        <v>0.4173823583973701</v>
       </c>
       <c r="G4" t="n">
-        <v>9.394484915689429</v>
+        <v>12.55925085155194</v>
       </c>
       <c r="H4" t="n">
-        <v>5.273342009853708</v>
+        <v>5.178321841652773</v>
       </c>
       <c r="I4" t="n">
-        <v>5.104052138219193</v>
+        <v>1.021569612662505</v>
       </c>
       <c r="J4" t="n">
-        <v>1.218727222321652</v>
+        <v>1.121180344975525</v>
       </c>
       <c r="K4" t="n">
-        <v>6.966668014552873</v>
+        <v>1.33618736378234</v>
       </c>
       <c r="L4" t="n">
-        <v>2.778170507924004</v>
+        <v>2.854632633441178</v>
       </c>
       <c r="M4" t="n">
-        <v>1.24966283736675</v>
+        <v>1.281260065090732</v>
       </c>
       <c r="N4" t="n">
-        <v>1.784450449312188</v>
+        <v>1.797795389039257</v>
       </c>
       <c r="O4" t="n">
         <v>104.65</v>
@@ -1081,7 +1072,7 @@
         <v>0.35</v>
       </c>
       <c r="S4" t="n">
-        <v>4.997891038021372</v>
+        <v>3.002066677880302</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1090,141 +1081,138 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>87.95629624933953</v>
+        <v>22.75389255227185</v>
       </c>
       <c r="W4" t="n">
         <v>100000</v>
       </c>
       <c r="X4" t="n">
-        <v>2.348663327355036</v>
+        <v>37.60921230635203</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4222866559344181</v>
+        <v>57.49433090736832</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03974249251445352</v>
+        <v>0.2294704473975079</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001745736782284338</v>
+        <v>0.01192406640348045</v>
       </c>
       <c r="AB4" t="n">
+        <v>0.5144968073786407</v>
+      </c>
+      <c r="AC4" t="n">
         <v>0.7</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
+        <v>14.20843610689675</v>
+      </c>
+      <c r="AE4" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD4" t="n">
-        <v>0.002345455738722631</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>47.29361854425881</v>
-      </c>
       <c r="AF4" t="n">
-        <v>15.04798072481444</v>
+        <v>0.02063748562958135</v>
       </c>
       <c r="AG4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="AI4" t="n">
         <v>0.001</v>
       </c>
-      <c r="AH4" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AI4" t="n">
+      <c r="AJ4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK4" t="n">
         <v>0.83</v>
       </c>
-      <c r="AJ4" t="n">
-        <v>1.95980314550334</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>5.555394637208996</v>
-      </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.54992195129251</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.926752071628995</v>
+        <v>3.730402357106044</v>
       </c>
       <c r="AN4" t="n">
-        <v>18.14753864329628</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>4</v>
+        <v>4.576502484691244</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.11</v>
+        <v>24.08990746867579</v>
       </c>
       <c r="AQ4" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AT4" t="n">
         <v>1.3</v>
       </c>
-      <c r="AR4" t="n">
-        <v>1.38785899595586</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>47.30682491754626</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.507634281406549</v>
-      </c>
       <c r="AU4" t="n">
-        <v>29.17872262816992</v>
+        <v>72.43186023054855</v>
       </c>
       <c r="AV4" t="n">
-        <v>18.1936222873824</v>
+        <v>5.786560425283344</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.857538550377192</v>
+        <v>3.911643615410707</v>
       </c>
       <c r="AX4" t="n">
-        <v>125</v>
+        <v>10.21558666895014</v>
       </c>
       <c r="AY4" t="n">
-        <v>58</v>
+        <v>27.22246315353338</v>
       </c>
       <c r="AZ4" t="n">
-        <v>971</v>
+        <v>7.4510253942797</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.037</v>
+        <v>-1.619</v>
       </c>
       <c r="BB4" t="n">
-        <v>756</v>
+        <v>8592</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.516</v>
+        <v>0.0015</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.165</v>
+        <v>1769.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>1769.8</v>
+        <v>258.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>258.5</v>
+        <v>0.234</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.234</v>
+        <v>7.785</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.785</v>
+        <v>0.15</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.15</v>
+        <v>1.36</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.36</v>
+        <v>72.47799999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>72.47799999999999</v>
+        <v>0.131</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.131</v>
+        <v>22.034</v>
       </c>
       <c r="BM4" t="n">
-        <v>22.034</v>
+        <v>3.284</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.284</v>
-      </c>
-      <c r="BO4" t="n">
         <v>35.752</v>
       </c>
     </row>
@@ -1233,43 +1221,43 @@
         <v>24</v>
       </c>
       <c r="B5" t="n">
-        <v>81.70344380782399</v>
+        <v>46.69718222109519</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02914083410769584</v>
+        <v>0.07420141093136294</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1027769907738974</v>
+        <v>0.1353130640802513</v>
       </c>
       <c r="E5" t="n">
-        <v>2.835734535550373</v>
+        <v>6.714982447612623</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01460426442196289</v>
+        <v>0.03261997875588642</v>
       </c>
       <c r="G5" t="n">
-        <v>28.98516456635008</v>
+        <v>6.814382941250751</v>
       </c>
       <c r="H5" t="n">
-        <v>2.820876156987032</v>
+        <v>6.402830730616826</v>
       </c>
       <c r="I5" t="n">
-        <v>4.793334898707079</v>
+        <v>5.948551504840317</v>
       </c>
       <c r="J5" t="n">
-        <v>3.768913731242999</v>
+        <v>2.365405211545907</v>
       </c>
       <c r="K5" t="n">
-        <v>1.485220272111878</v>
+        <v>7.365725652037398</v>
       </c>
       <c r="L5" t="n">
-        <v>1.144756878397239</v>
+        <v>5.400355754753201</v>
       </c>
       <c r="M5" t="n">
-        <v>3.066522490478216</v>
+        <v>3.603129291523899</v>
       </c>
       <c r="N5" t="n">
-        <v>1.594028811724696</v>
+        <v>6.276711359372106</v>
       </c>
       <c r="O5" t="n">
         <v>104.65</v>
@@ -1284,7 +1272,7 @@
         <v>0.35</v>
       </c>
       <c r="S5" t="n">
-        <v>1.806574315452508</v>
+        <v>2.283606361057529</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1293,141 +1281,138 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.869748199744532</v>
+        <v>1.283642687648207</v>
       </c>
       <c r="W5" t="n">
         <v>100000</v>
       </c>
       <c r="X5" t="n">
-        <v>29.65393054243909</v>
+        <v>11.24174233034105</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.009888170906755261</v>
+        <v>44.83698397173242</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.1715849544091614</v>
+        <v>0.004044198750904273</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.07901698818809073</v>
+        <v>0.001031634961988427</v>
       </c>
       <c r="AB5" t="n">
+        <v>0.102577627397502</v>
+      </c>
+      <c r="AC5" t="n">
         <v>0.7</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
+        <v>10.51275898504271</v>
+      </c>
+      <c r="AE5" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD5" t="n">
-        <v>0.0589051498733489</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>47.14705239285698</v>
-      </c>
       <c r="AF5" t="n">
-        <v>25.05588263029578</v>
+        <v>0.006426047431207881</v>
       </c>
       <c r="AG5" t="n">
+        <v>48</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="AI5" t="n">
         <v>0.001</v>
       </c>
-      <c r="AH5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AI5" t="n">
+      <c r="AJ5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK5" t="n">
         <v>0.83</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>4.123597626033926</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2.94804974202122</v>
-      </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.743298886748432</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.367469136529979</v>
+        <v>2.231426452964624</v>
       </c>
       <c r="AN5" t="n">
-        <v>16.40295919398157</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>5</v>
+        <v>1.080116960329074</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.11</v>
+        <v>24.78187691698542</v>
       </c>
       <c r="AQ5" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AT5" t="n">
         <v>1.3</v>
       </c>
-      <c r="AR5" t="n">
-        <v>1.153811562099243</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.137939529830414</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.007262756369808</v>
-      </c>
       <c r="AU5" t="n">
-        <v>23.16712766072778</v>
+        <v>46.14645233072311</v>
       </c>
       <c r="AV5" t="n">
-        <v>20.19739516855509</v>
+        <v>6.783215054810987</v>
       </c>
       <c r="AW5" t="n">
-        <v>14.51458998054649</v>
+        <v>1.427310939303219</v>
       </c>
       <c r="AX5" t="n">
-        <v>125</v>
+        <v>123.5368337606679</v>
       </c>
       <c r="AY5" t="n">
-        <v>58</v>
+        <v>276.3224397968215</v>
       </c>
       <c r="AZ5" t="n">
-        <v>971</v>
+        <v>3.92613753973206</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.037</v>
+        <v>-1.619</v>
       </c>
       <c r="BB5" t="n">
-        <v>756</v>
+        <v>8592</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.516</v>
+        <v>0.0015</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.165</v>
+        <v>1769.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>1769.8</v>
+        <v>258.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>258.5</v>
+        <v>0.234</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.234</v>
+        <v>7.785</v>
       </c>
       <c r="BH5" t="n">
-        <v>7.785</v>
+        <v>0.15</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.15</v>
+        <v>1.36</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1.36</v>
+        <v>72.47799999999999</v>
       </c>
       <c r="BK5" t="n">
-        <v>72.47799999999999</v>
+        <v>0.131</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.131</v>
+        <v>22.034</v>
       </c>
       <c r="BM5" t="n">
-        <v>22.034</v>
+        <v>3.284</v>
       </c>
       <c r="BN5" t="n">
-        <v>3.284</v>
-      </c>
-      <c r="BO5" t="n">
         <v>35.752</v>
       </c>
     </row>
@@ -1436,43 +1421,43 @@
         <v>24</v>
       </c>
       <c r="B6" t="n">
-        <v>71.59997520816098</v>
+        <v>9.379756640813595</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4713234354855512</v>
+        <v>0.04900632105981607</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001123072977021321</v>
+        <v>0.2758505857009971</v>
       </c>
       <c r="E6" t="n">
-        <v>29.06296971243342</v>
+        <v>4.049135095720916</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1693336587445884</v>
+        <v>0.02590140148178926</v>
       </c>
       <c r="G6" t="n">
-        <v>9.610708064832668</v>
+        <v>5.906680194603794</v>
       </c>
       <c r="H6" t="n">
-        <v>5.505549700575867</v>
+        <v>6.614484465962155</v>
       </c>
       <c r="I6" t="n">
-        <v>2.610280895821241</v>
+        <v>2.712869371728964</v>
       </c>
       <c r="J6" t="n">
-        <v>2.968116016248898</v>
+        <v>2.226880573178217</v>
       </c>
       <c r="K6" t="n">
-        <v>2.444166673814034</v>
+        <v>4.117205688206125</v>
       </c>
       <c r="L6" t="n">
-        <v>4.504986688703847</v>
+        <v>1.458433271129259</v>
       </c>
       <c r="M6" t="n">
-        <v>1.183763443568245</v>
+        <v>6.142424354023477</v>
       </c>
       <c r="N6" t="n">
-        <v>1.054083269617909</v>
+        <v>5.095866576101984</v>
       </c>
       <c r="O6" t="n">
         <v>104.65</v>
@@ -1487,7 +1472,7 @@
         <v>0.35</v>
       </c>
       <c r="S6" t="n">
-        <v>3.989182893810989</v>
+        <v>7.270300853488886</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1496,141 +1481,138 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>3.165357962291968</v>
+        <v>99.24384993313751</v>
       </c>
       <c r="W6" t="n">
         <v>100000</v>
       </c>
       <c r="X6" t="n">
-        <v>28.39387914082847</v>
+        <v>10.38856368522962</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.01730404353339971</v>
+        <v>34.44222699819939</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.003071413917709199</v>
+        <v>0.06710508758370076</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.02035408847561737</v>
+        <v>0.5795125637606151</v>
       </c>
       <c r="AB6" t="n">
+        <v>0.02084850806159703</v>
+      </c>
+      <c r="AC6" t="n">
         <v>0.7</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
+        <v>52.9696194877612</v>
+      </c>
+      <c r="AE6" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD6" t="n">
-        <v>0.001639794721172315</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>47.50275398145985</v>
-      </c>
       <c r="AF6" t="n">
-        <v>43.47096254919236</v>
+        <v>0.08809843300322953</v>
       </c>
       <c r="AG6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="AI6" t="n">
         <v>0.001</v>
       </c>
-      <c r="AH6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AI6" t="n">
+      <c r="AJ6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK6" t="n">
         <v>0.83</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>3.444895206166115</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>7.436825485097111</v>
-      </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.246830546567619</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.494465645319397</v>
+        <v>3.432397551411651</v>
       </c>
       <c r="AN6" t="n">
-        <v>33.91589984623916</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>3</v>
+        <v>3.31593357791691</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.11</v>
+        <v>54.37699568918521</v>
       </c>
       <c r="AQ6" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AT6" t="n">
         <v>1.3</v>
       </c>
-      <c r="AR6" t="n">
-        <v>4.021552612647521</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>32.70365599215324</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>11.44806176435208</v>
-      </c>
       <c r="AU6" t="n">
-        <v>8.982854933973281</v>
+        <v>9.5807949076246</v>
       </c>
       <c r="AV6" t="n">
-        <v>6.107183347366915</v>
+        <v>7.33567480326589</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.667885716107302</v>
+        <v>1.12439022003546</v>
       </c>
       <c r="AX6" t="n">
-        <v>125</v>
+        <v>24.11680706554161</v>
       </c>
       <c r="AY6" t="n">
-        <v>58</v>
+        <v>6.021146309727622</v>
       </c>
       <c r="AZ6" t="n">
-        <v>971</v>
+        <v>3.422230146706039</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.037</v>
+        <v>-1.619</v>
       </c>
       <c r="BB6" t="n">
-        <v>756</v>
+        <v>8592</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.516</v>
+        <v>0.0015</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.165</v>
+        <v>1769.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>1769.8</v>
+        <v>258.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>258.5</v>
+        <v>0.234</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.234</v>
+        <v>7.785</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.785</v>
+        <v>0.15</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.15</v>
+        <v>1.36</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1.36</v>
+        <v>72.47799999999999</v>
       </c>
       <c r="BK6" t="n">
-        <v>72.47799999999999</v>
+        <v>0.131</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.131</v>
+        <v>22.034</v>
       </c>
       <c r="BM6" t="n">
-        <v>22.034</v>
+        <v>3.284</v>
       </c>
       <c r="BN6" t="n">
-        <v>3.284</v>
-      </c>
-      <c r="BO6" t="n">
         <v>35.752</v>
       </c>
     </row>
@@ -1639,43 +1621,43 @@
         <v>24</v>
       </c>
       <c r="B7" t="n">
-        <v>9.186445702863717</v>
+        <v>22.26436999960995</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01032206354898273</v>
+        <v>0.1599870997400225</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2375197118155644</v>
+        <v>0.0512903051507248</v>
       </c>
       <c r="E7" t="n">
-        <v>2.52278417315205</v>
+        <v>12.43419079427586</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002161220282973304</v>
+        <v>0.04593744862133514</v>
       </c>
       <c r="G7" t="n">
-        <v>2.248998562279267</v>
+        <v>13.99454945346006</v>
       </c>
       <c r="H7" t="n">
-        <v>9.102540228882535</v>
+        <v>3.931323401086662</v>
       </c>
       <c r="I7" t="n">
-        <v>1.853054636676905</v>
+        <v>2.26530018196526</v>
       </c>
       <c r="J7" t="n">
-        <v>9.10302970523896</v>
+        <v>2.950773292384493</v>
       </c>
       <c r="K7" t="n">
-        <v>2.105929227621635</v>
+        <v>1.498175194398025</v>
       </c>
       <c r="L7" t="n">
-        <v>5.819589918853242</v>
+        <v>3.536088413471687</v>
       </c>
       <c r="M7" t="n">
-        <v>1.742167138335173</v>
+        <v>3.879192369533134</v>
       </c>
       <c r="N7" t="n">
-        <v>3.113126221140558</v>
+        <v>7.061239365219629</v>
       </c>
       <c r="O7" t="n">
         <v>104.65</v>
@@ -1690,7 +1672,7 @@
         <v>0.35</v>
       </c>
       <c r="S7" t="n">
-        <v>2.510858693993427</v>
+        <v>1.016769260860242</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1699,141 +1681,138 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>33.19911264233838</v>
+        <v>16.54422483920433</v>
       </c>
       <c r="W7" t="n">
         <v>100000</v>
       </c>
       <c r="X7" t="n">
-        <v>96.58048601021434</v>
+        <v>2.387972243637805</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.2497150465602352</v>
+        <v>51.73819204479792</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0158615657712303</v>
+        <v>0.2376568827345656</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.720266146012741</v>
+        <v>0.003083411745237574</v>
       </c>
       <c r="AB7" t="n">
+        <v>3.140117753746788</v>
+      </c>
+      <c r="AC7" t="n">
         <v>0.7</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
+        <v>56.13455789085592</v>
+      </c>
+      <c r="AE7" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD7" t="n">
-        <v>0.003460449375175034</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>48.61410445458024</v>
-      </c>
       <c r="AF7" t="n">
-        <v>92.17707203103545</v>
+        <v>0.04374823466826643</v>
       </c>
       <c r="AG7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="AI7" t="n">
         <v>0.001</v>
       </c>
-      <c r="AH7" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AI7" t="n">
+      <c r="AJ7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK7" t="n">
         <v>0.83</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>1.398734409166407</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.948874309869082</v>
-      </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.142461814743003</v>
       </c>
       <c r="AM7" t="n">
-        <v>3.683134612424339</v>
+        <v>3.887162640672961</v>
       </c>
       <c r="AN7" t="n">
-        <v>28.75492846884335</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>2</v>
+        <v>2.607233820496676</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.11</v>
+        <v>13.42913364204331</v>
       </c>
       <c r="AQ7" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AT7" t="n">
         <v>1.3</v>
       </c>
-      <c r="AR7" t="n">
-        <v>1.346778181016357</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>52.42200216785555</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0.6078972276628447</v>
-      </c>
       <c r="AU7" t="n">
-        <v>4.646894312856268</v>
+        <v>1.631317218677692</v>
       </c>
       <c r="AV7" t="n">
-        <v>81.014832571832</v>
+        <v>5.277731129056606</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.61369853923949</v>
+        <v>3.64641744961789</v>
       </c>
       <c r="AX7" t="n">
-        <v>125</v>
+        <v>5.333956283429139</v>
       </c>
       <c r="AY7" t="n">
-        <v>58</v>
+        <v>53.76800988043918</v>
       </c>
       <c r="AZ7" t="n">
-        <v>971</v>
+        <v>19.14487533303477</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.037</v>
+        <v>-1.619</v>
       </c>
       <c r="BB7" t="n">
-        <v>756</v>
+        <v>8592</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.516</v>
+        <v>0.0015</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.165</v>
+        <v>1769.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>1769.8</v>
+        <v>258.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>258.5</v>
+        <v>0.234</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.234</v>
+        <v>7.785</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.785</v>
+        <v>0.15</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.15</v>
+        <v>1.36</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1.36</v>
+        <v>72.47799999999999</v>
       </c>
       <c r="BK7" t="n">
-        <v>72.47799999999999</v>
+        <v>0.131</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.131</v>
+        <v>22.034</v>
       </c>
       <c r="BM7" t="n">
-        <v>22.034</v>
+        <v>3.284</v>
       </c>
       <c r="BN7" t="n">
-        <v>3.284</v>
-      </c>
-      <c r="BO7" t="n">
         <v>35.752</v>
       </c>
     </row>
@@ -1842,43 +1821,43 @@
         <v>24</v>
       </c>
       <c r="B8" t="n">
-        <v>12.55457780708516</v>
+        <v>56.77545300639991</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02440400417329082</v>
+        <v>0.01071170710580024</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01193365678652883</v>
+        <v>0.0739490015452639</v>
       </c>
       <c r="E8" t="n">
-        <v>4.506903875271743</v>
+        <v>37.01906129860612</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001081817882316223</v>
+        <v>0.0122894067912696</v>
       </c>
       <c r="G8" t="n">
-        <v>4.910917394889776</v>
+        <v>7.230620405658603</v>
       </c>
       <c r="H8" t="n">
-        <v>5.295639365320477</v>
+        <v>2.756867375922956</v>
       </c>
       <c r="I8" t="n">
-        <v>2.831065775285251</v>
+        <v>2.913276271000146</v>
       </c>
       <c r="J8" t="n">
-        <v>9.762022725866105</v>
+        <v>7.82741970757138</v>
       </c>
       <c r="K8" t="n">
-        <v>6.82391532362838</v>
+        <v>1.388757555318234</v>
       </c>
       <c r="L8" t="n">
-        <v>3.684173951304885</v>
+        <v>3.999284954612539</v>
       </c>
       <c r="M8" t="n">
-        <v>2.176941016983656</v>
+        <v>3.429059660882014</v>
       </c>
       <c r="N8" t="n">
-        <v>5.541974902915644</v>
+        <v>1.752949853462382</v>
       </c>
       <c r="O8" t="n">
         <v>104.65</v>
@@ -1893,7 +1872,7 @@
         <v>0.35</v>
       </c>
       <c r="S8" t="n">
-        <v>4.721124517422286</v>
+        <v>2.261444933739939</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1902,141 +1881,138 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>97.02869812145943</v>
+        <v>1.195821387053563</v>
       </c>
       <c r="W8" t="n">
         <v>100000</v>
       </c>
       <c r="X8" t="n">
-        <v>89.82428950212662</v>
+        <v>64.36969806645946</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.001140559468180493</v>
+        <v>54.15416013175602</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0202603325920751</v>
+        <v>0.001692272973570823</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.455391320007288</v>
+        <v>0.003065965399039811</v>
       </c>
       <c r="AB8" t="n">
+        <v>0.02235368091690499</v>
+      </c>
+      <c r="AC8" t="n">
         <v>0.7</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
+        <v>26.65093391855495</v>
+      </c>
+      <c r="AE8" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD8" t="n">
-        <v>0.02170406471053715</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>47.92634481160338</v>
-      </c>
       <c r="AF8" t="n">
-        <v>78.42976802373988</v>
+        <v>0.6272563328767455</v>
       </c>
       <c r="AG8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="AI8" t="n">
         <v>0.001</v>
       </c>
-      <c r="AH8" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AI8" t="n">
+      <c r="AJ8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK8" t="n">
         <v>0.83</v>
       </c>
-      <c r="AJ8" t="n">
-        <v>1.229876766661705</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>9.778917803726236</v>
-      </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.897150388623759</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.056081010001009</v>
+        <v>4.503010411561246</v>
       </c>
       <c r="AN8" t="n">
-        <v>38.99793322949121</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.5</v>
+        <v>3.718185409093903</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.11</v>
+        <v>30.46188375698856</v>
       </c>
       <c r="AQ8" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AT8" t="n">
         <v>1.3</v>
       </c>
-      <c r="AR8" t="n">
-        <v>45.37272227579796</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.892548459437771</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.226224420022519</v>
-      </c>
       <c r="AU8" t="n">
-        <v>82.92124224464152</v>
+        <v>1.829865371408276</v>
       </c>
       <c r="AV8" t="n">
-        <v>64.03776639300786</v>
+        <v>2.246609816812063</v>
       </c>
       <c r="AW8" t="n">
-        <v>43.05728709072634</v>
+        <v>3.386246596696959</v>
       </c>
       <c r="AX8" t="n">
-        <v>125</v>
+        <v>12.79404090775655</v>
       </c>
       <c r="AY8" t="n">
-        <v>58</v>
+        <v>7.31176265391078</v>
       </c>
       <c r="AZ8" t="n">
-        <v>971</v>
+        <v>53.27406743927168</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.037</v>
+        <v>-1.619</v>
       </c>
       <c r="BB8" t="n">
-        <v>756</v>
+        <v>8592</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.516</v>
+        <v>0.0015</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.165</v>
+        <v>1769.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>1769.8</v>
+        <v>258.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>258.5</v>
+        <v>0.234</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.234</v>
+        <v>7.785</v>
       </c>
       <c r="BH8" t="n">
-        <v>7.785</v>
+        <v>0.15</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.15</v>
+        <v>1.36</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1.36</v>
+        <v>72.47799999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>72.47799999999999</v>
+        <v>0.131</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.131</v>
+        <v>22.034</v>
       </c>
       <c r="BM8" t="n">
-        <v>22.034</v>
+        <v>3.284</v>
       </c>
       <c r="BN8" t="n">
-        <v>3.284</v>
-      </c>
-      <c r="BO8" t="n">
         <v>35.752</v>
       </c>
     </row>
@@ -2045,43 +2021,43 @@
         <v>24</v>
       </c>
       <c r="B9" t="n">
-        <v>3.281320096265449</v>
+        <v>20.01949168566397</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02386117648056063</v>
+        <v>0.1436804419289488</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4756871003239136</v>
+        <v>0.2138589082388256</v>
       </c>
       <c r="E9" t="n">
-        <v>42.09314417133456</v>
+        <v>14.39717970164245</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01429446333064133</v>
+        <v>0.1019894429444134</v>
       </c>
       <c r="G9" t="n">
-        <v>43.86540292809647</v>
+        <v>48.1179589435061</v>
       </c>
       <c r="H9" t="n">
-        <v>3.636749461657438</v>
+        <v>2.761309244512625</v>
       </c>
       <c r="I9" t="n">
-        <v>4.711320208388512</v>
+        <v>1.92969787230581</v>
       </c>
       <c r="J9" t="n">
-        <v>3.546793296257681</v>
+        <v>2.131333689778582</v>
       </c>
       <c r="K9" t="n">
-        <v>9.404436005960278</v>
+        <v>9.092512392971699</v>
       </c>
       <c r="L9" t="n">
-        <v>2.091382132446103</v>
+        <v>8.392837476277311</v>
       </c>
       <c r="M9" t="n">
-        <v>4.709026922721673</v>
+        <v>2.120554839962668</v>
       </c>
       <c r="N9" t="n">
-        <v>7.08218903556156</v>
+        <v>9.078529622329023</v>
       </c>
       <c r="O9" t="n">
         <v>104.65</v>
@@ -2096,7 +2072,7 @@
         <v>0.35</v>
       </c>
       <c r="S9" t="n">
-        <v>1.905075102455216</v>
+        <v>4.171675229446766</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -2105,141 +2081,138 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>2.372978136105307</v>
+        <v>7.422267056456102</v>
       </c>
       <c r="W9" t="n">
         <v>100000</v>
       </c>
       <c r="X9" t="n">
-        <v>23.19407992596669</v>
+        <v>80.93766884683811</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.2258793204008973</v>
+        <v>63.35757310054579</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0014582770280177</v>
+        <v>0.02069788787165764</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01072207797397361</v>
+        <v>0.07518050746424822</v>
       </c>
       <c r="AB9" t="n">
+        <v>3.685612615751735</v>
+      </c>
+      <c r="AC9" t="n">
         <v>0.7</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
+        <v>66.15690431092681</v>
+      </c>
+      <c r="AE9" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD9" t="n">
-        <v>0.230932620613085</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>47.59653666605058</v>
-      </c>
       <c r="AF9" t="n">
-        <v>15.50059527448968</v>
+        <v>0.0092313316697957</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001</v>
+        <v>48</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.11</v>
+        <v>30.46</v>
       </c>
       <c r="AI9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK9" t="n">
         <v>0.83</v>
       </c>
-      <c r="AJ9" t="n">
-        <v>3.63751890672659</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>7.005537602244284</v>
-      </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.669920341738279</v>
       </c>
       <c r="AM9" t="n">
-        <v>5.284760147272462</v>
+        <v>1.702588185887329</v>
       </c>
       <c r="AN9" t="n">
-        <v>33.61371478103343</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>1</v>
+        <v>1.239932294418709</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.11</v>
+        <v>11.66906657823577</v>
       </c>
       <c r="AQ9" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AT9" t="n">
         <v>1.3</v>
       </c>
-      <c r="AR9" t="n">
-        <v>1.7094459041939</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>44.09172266547928</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0.4870679516534446</v>
-      </c>
       <c r="AU9" t="n">
-        <v>21.27794827688885</v>
+        <v>12.54411160596529</v>
       </c>
       <c r="AV9" t="n">
-        <v>30.89346060897748</v>
+        <v>11.17116906361924</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.890901836621649</v>
+        <v>11.13732848695389</v>
       </c>
       <c r="AX9" t="n">
-        <v>125</v>
+        <v>18.81370721522565</v>
       </c>
       <c r="AY9" t="n">
-        <v>58</v>
+        <v>128.6662553710724</v>
       </c>
       <c r="AZ9" t="n">
-        <v>971</v>
+        <v>12.72225937417835</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.037</v>
+        <v>-1.619</v>
       </c>
       <c r="BB9" t="n">
-        <v>756</v>
+        <v>8592</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.516</v>
+        <v>0.0015</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.165</v>
+        <v>1769.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>1769.8</v>
+        <v>258.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>258.5</v>
+        <v>0.234</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.234</v>
+        <v>7.785</v>
       </c>
       <c r="BH9" t="n">
-        <v>7.785</v>
+        <v>0.15</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.15</v>
+        <v>1.36</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1.36</v>
+        <v>72.47799999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>72.47799999999999</v>
+        <v>0.131</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.131</v>
+        <v>22.034</v>
       </c>
       <c r="BM9" t="n">
-        <v>22.034</v>
+        <v>3.284</v>
       </c>
       <c r="BN9" t="n">
-        <v>3.284</v>
-      </c>
-      <c r="BO9" t="n">
         <v>35.752</v>
       </c>
     </row>
@@ -2248,43 +2221,43 @@
         <v>24</v>
       </c>
       <c r="B10" t="n">
-        <v>17.91773596912573</v>
+        <v>4.589256542102138</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1826303767697921</v>
+        <v>0.04348574000766144</v>
       </c>
       <c r="D10" t="n">
-        <v>0.05486131502691064</v>
+        <v>0.3615194732580368</v>
       </c>
       <c r="E10" t="n">
-        <v>2.037023944257305</v>
+        <v>3.013501058523384</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02675161948285869</v>
+        <v>0.003423970761123295</v>
       </c>
       <c r="G10" t="n">
-        <v>3.181959892514387</v>
+        <v>1.110597121341366</v>
       </c>
       <c r="H10" t="n">
-        <v>6.805342573804791</v>
+        <v>5.126955094120341</v>
       </c>
       <c r="I10" t="n">
-        <v>3.135079376896272</v>
+        <v>1.716000206334606</v>
       </c>
       <c r="J10" t="n">
-        <v>2.379107583299622</v>
+        <v>6.146310239665764</v>
       </c>
       <c r="K10" t="n">
-        <v>4.22184533988398</v>
+        <v>1.063124498704862</v>
       </c>
       <c r="L10" t="n">
-        <v>1.173537986594373</v>
+        <v>7.121107058722164</v>
       </c>
       <c r="M10" t="n">
-        <v>1.719762024872556</v>
+        <v>1.685314624062074</v>
       </c>
       <c r="N10" t="n">
-        <v>2.310478898298407</v>
+        <v>6.576131603937956</v>
       </c>
       <c r="O10" t="n">
         <v>104.65</v>
@@ -2299,7 +2272,7 @@
         <v>0.35</v>
       </c>
       <c r="S10" t="n">
-        <v>1.742274011694833</v>
+        <v>2.969737971146087</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -2308,141 +2281,138 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>24.56696209538416</v>
+        <v>21.75614729232993</v>
       </c>
       <c r="W10" t="n">
         <v>100000</v>
       </c>
       <c r="X10" t="n">
-        <v>4.055155578091554</v>
+        <v>26.92800277386486</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.1317603781012531</v>
+        <v>34.96175927353148</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01664471254655459</v>
+        <v>0.09645365858237577</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.2689754796203033</v>
+        <v>0.007268280701694626</v>
       </c>
       <c r="AB10" t="n">
+        <v>0.03423391087458417</v>
+      </c>
+      <c r="AC10" t="n">
         <v>0.7</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
+        <v>23.21070577352978</v>
+      </c>
+      <c r="AE10" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD10" t="n">
-        <v>0.003417769519140669</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>47.81428710873787</v>
-      </c>
       <c r="AF10" t="n">
-        <v>17.92669840983086</v>
+        <v>0.007106420083834219</v>
       </c>
       <c r="AG10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>30.46</v>
+      </c>
+      <c r="AI10" t="n">
         <v>0.001</v>
       </c>
-      <c r="AH10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AI10" t="n">
+      <c r="AJ10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AK10" t="n">
         <v>0.83</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>3.331302081669874</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.511690506826077</v>
-      </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>2.382250382224053</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.285971123125979</v>
+        <v>1.063733589456633</v>
       </c>
       <c r="AN10" t="n">
-        <v>30.82536353418623</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
+        <v>5.542282003599244</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>13.392155232207</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="AR10" t="n">
         <v>1.5</v>
       </c>
-      <c r="AP10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AQ10" t="n">
+      <c r="AS10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AT10" t="n">
         <v>1.3</v>
       </c>
-      <c r="AR10" t="n">
-        <v>1.092091572934176</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>10.73637355985257</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0.9754019880475571</v>
-      </c>
       <c r="AU10" t="n">
-        <v>8.329316792834856</v>
+        <v>9.696617094738414</v>
       </c>
       <c r="AV10" t="n">
-        <v>23.8528027502881</v>
+        <v>50.57839252531996</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.861640185317263</v>
+        <v>0.4932942192452344</v>
       </c>
       <c r="AX10" t="n">
-        <v>125</v>
+        <v>145.2180167872444</v>
       </c>
       <c r="AY10" t="n">
-        <v>58</v>
+        <v>9.775290035472889</v>
       </c>
       <c r="AZ10" t="n">
-        <v>971</v>
+        <v>154.3614975696017</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.037</v>
+        <v>-1.619</v>
       </c>
       <c r="BB10" t="n">
-        <v>756</v>
+        <v>8592</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.516</v>
+        <v>0.0015</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.165</v>
+        <v>1769.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>1769.8</v>
+        <v>258.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>258.5</v>
+        <v>0.234</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.234</v>
+        <v>7.785</v>
       </c>
       <c r="BH10" t="n">
-        <v>7.785</v>
+        <v>0.15</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.15</v>
+        <v>1.36</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.36</v>
+        <v>72.47799999999999</v>
       </c>
       <c r="BK10" t="n">
-        <v>72.47799999999999</v>
+        <v>0.131</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.131</v>
+        <v>22.034</v>
       </c>
       <c r="BM10" t="n">
-        <v>22.034</v>
+        <v>3.284</v>
       </c>
       <c r="BN10" t="n">
-        <v>3.284</v>
-      </c>
-      <c r="BO10" t="n">
         <v>35.752</v>
       </c>
     </row>

--- a/input_home.xlsx
+++ b/input_home.xlsx
@@ -421,49 +421,49 @@
         <v>24</v>
       </c>
       <c r="B1" t="n">
-        <v>1.032413632074936</v>
+        <v>21.08280781737069</v>
       </c>
       <c r="C1" t="n">
-        <v>0.1627898208626276</v>
+        <v>0.09138178310500439</v>
       </c>
       <c r="D1" t="n">
-        <v>0.1196648226375569</v>
+        <v>0.3402716441383726</v>
       </c>
       <c r="E1" t="n">
-        <v>1.020956344358439</v>
+        <v>1.483605087826981</v>
       </c>
       <c r="F1" t="n">
-        <v>0.07770982650554237</v>
+        <v>0.02634415766252343</v>
       </c>
       <c r="G1" t="n">
-        <v>3.367334079913048</v>
+        <v>24.01750891658013</v>
       </c>
       <c r="H1" t="n">
-        <v>1.63201338142251</v>
+        <v>3.680181500975511</v>
       </c>
       <c r="I1" t="n">
-        <v>1.230155036060779</v>
+        <v>2.108450680760779</v>
       </c>
       <c r="J1" t="n">
-        <v>1.348639631823085</v>
+        <v>3.089077785617069</v>
       </c>
       <c r="K1" t="n">
-        <v>2.987344514790534</v>
+        <v>2.826370154346388</v>
       </c>
       <c r="L1" t="n">
-        <v>1.497755566071609</v>
+        <v>1.704695450324314</v>
       </c>
       <c r="M1" t="n">
-        <v>1.170112765755061</v>
+        <v>3.026294427652643</v>
       </c>
       <c r="N1" t="n">
-        <v>1.203321991766221</v>
+        <v>3.2225562496091</v>
       </c>
       <c r="O1" t="n">
         <v>104.65</v>
       </c>
       <c r="P1" t="n">
-        <v>0.001</v>
+        <v>0.5</v>
       </c>
       <c r="Q1" t="n">
         <v>0.11</v>
@@ -472,7 +472,7 @@
         <v>0.35</v>
       </c>
       <c r="S1" t="n">
-        <v>8.61074547318446</v>
+        <v>5.270588844336339</v>
       </c>
       <c r="T1" t="n">
         <v>0</v>
@@ -481,37 +481,37 @@
         <v>0</v>
       </c>
       <c r="V1" t="n">
-        <v>9.747697013980572</v>
+        <v>83.10452360132291</v>
       </c>
       <c r="W1" t="n">
         <v>100000</v>
       </c>
       <c r="X1" t="n">
-        <v>64.21046252755066</v>
+        <v>2.244385906775219</v>
       </c>
       <c r="Y1" t="n">
-        <v>17.42673283862688</v>
+        <v>61.60458904900389</v>
       </c>
       <c r="Z1" t="n">
-        <v>0.05221288872023668</v>
+        <v>0.04500534761979962</v>
       </c>
       <c r="AA1" t="n">
-        <v>0.002085619146137659</v>
+        <v>0.3616321008050632</v>
       </c>
       <c r="AB1" t="n">
-        <v>0.4692052871403969</v>
+        <v>0.1007899881956241</v>
       </c>
       <c r="AC1" t="n">
         <v>0.7</v>
       </c>
       <c r="AD1" t="n">
-        <v>42.96149175985146</v>
+        <v>42.48556516645564</v>
       </c>
       <c r="AE1" t="n">
         <v>0.5</v>
       </c>
       <c r="AF1" t="n">
-        <v>0.003976913487032602</v>
+        <v>0.002154587783119306</v>
       </c>
       <c r="AG1" t="n">
         <v>48</v>
@@ -529,25 +529,25 @@
         <v>0.83</v>
       </c>
       <c r="AL1" t="n">
-        <v>7.411779338147104</v>
+        <v>4.18297707285801</v>
       </c>
       <c r="AM1" t="n">
-        <v>1.138267504610848</v>
+        <v>1.623169339276551</v>
       </c>
       <c r="AN1" t="n">
         <v>0</v>
       </c>
       <c r="AO1" t="n">
-        <v>1.529762337102114</v>
+        <v>2.74689479944312</v>
       </c>
       <c r="AP1" t="n">
-        <v>11.50023234397964</v>
+        <v>19.26936572477398</v>
       </c>
       <c r="AQ1" t="n">
         <v>15.31</v>
       </c>
       <c r="AR1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS1" t="n">
         <v>0.11</v>
@@ -556,22 +556,22 @@
         <v>1.3</v>
       </c>
       <c r="AU1" t="n">
-        <v>1.684705720618699</v>
+        <v>96.71368604447255</v>
       </c>
       <c r="AV1" t="n">
-        <v>3.297185736888111</v>
+        <v>1.632988112504921</v>
       </c>
       <c r="AW1" t="n">
-        <v>0.5380533171678058</v>
+        <v>0.3800239630148674</v>
       </c>
       <c r="AX1" t="n">
-        <v>160.6894578221434</v>
+        <v>88.65705935882808</v>
       </c>
       <c r="AY1" t="n">
-        <v>95.18306116072004</v>
+        <v>20.62588145825003</v>
       </c>
       <c r="AZ1" t="n">
-        <v>3.869204293167968</v>
+        <v>62.82354858990544</v>
       </c>
       <c r="BA1" t="n">
         <v>-1.619</v>
@@ -621,43 +621,43 @@
         <v>24</v>
       </c>
       <c r="B2" t="n">
-        <v>10.97308508631592</v>
+        <v>2.052317625358281</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0188306562847828</v>
+        <v>0.03321714991009268</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1702340922978603</v>
+        <v>0.4238354188208024</v>
       </c>
       <c r="E2" t="n">
-        <v>26.36198200399864</v>
+        <v>16.39121620536209</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007392736437210276</v>
+        <v>0.03330015943360494</v>
       </c>
       <c r="G2" t="n">
-        <v>6.885258895409383</v>
+        <v>1.354295336361108</v>
       </c>
       <c r="H2" t="n">
-        <v>1.089545254141308</v>
+        <v>5.980665894838839</v>
       </c>
       <c r="I2" t="n">
-        <v>6.014018694442155</v>
+        <v>1.302306694914315</v>
       </c>
       <c r="J2" t="n">
-        <v>9.684362664990585</v>
+        <v>6.531469336173868</v>
       </c>
       <c r="K2" t="n">
-        <v>1.456094600706738</v>
+        <v>3.970840513339755</v>
       </c>
       <c r="L2" t="n">
-        <v>2.559614803267043</v>
+        <v>3.25816580916512</v>
       </c>
       <c r="M2" t="n">
-        <v>1.317517210174703</v>
+        <v>1.94743993814401</v>
       </c>
       <c r="N2" t="n">
-        <v>2.210212638114107</v>
+        <v>3.540738210468991</v>
       </c>
       <c r="O2" t="n">
         <v>104.65</v>
@@ -672,7 +672,7 @@
         <v>0.35</v>
       </c>
       <c r="S2" t="n">
-        <v>2.255432812359252</v>
+        <v>3.311129326132998</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -681,37 +681,37 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>11.65431088556491</v>
+        <v>6.319459761491423</v>
       </c>
       <c r="W2" t="n">
         <v>100000</v>
       </c>
       <c r="X2" t="n">
-        <v>2.348233196562541</v>
+        <v>29.95387502568423</v>
       </c>
       <c r="Y2" t="n">
-        <v>29.16871394597773</v>
+        <v>54.76083510852956</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2144962563085203</v>
+        <v>0.01249250912443576</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1689326686933556</v>
+        <v>0.2742024247088334</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.005850230464798222</v>
+        <v>0.304008036011061</v>
       </c>
       <c r="AC2" t="n">
         <v>0.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>28.41256479776825</v>
+        <v>25.7878795684578</v>
       </c>
       <c r="AE2" t="n">
         <v>0.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.06208555535289812</v>
+        <v>0.0268053459161071</v>
       </c>
       <c r="AG2" t="n">
         <v>48</v>
@@ -720,7 +720,7 @@
         <v>30.46</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.5</v>
+        <v>0.001</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.11</v>
@@ -729,25 +729,25 @@
         <v>0.83</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.267011317589521</v>
+        <v>3.032505122652547</v>
       </c>
       <c r="AM2" t="n">
-        <v>3.661180961077433</v>
+        <v>5.134626703865262</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.610156867677722</v>
+        <v>1.605261181572286</v>
       </c>
       <c r="AP2" t="n">
-        <v>66.9284605735124</v>
+        <v>66.1738680371611</v>
       </c>
       <c r="AQ2" t="n">
         <v>15.31</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AS2" t="n">
         <v>0.11</v>
@@ -756,22 +756,22 @@
         <v>1.3</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.66340448511619</v>
+        <v>1.995346633609642</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.517765007345609</v>
+        <v>64.49842282834626</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.8620778279887347</v>
+        <v>24.40251436869462</v>
       </c>
       <c r="AX2" t="n">
-        <v>24.51490380254786</v>
+        <v>9.582352426946448</v>
       </c>
       <c r="AY2" t="n">
-        <v>89.07768174602847</v>
+        <v>48.4435297991561</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.847414214008011</v>
+        <v>10.92483256991497</v>
       </c>
       <c r="BA2" t="n">
         <v>-1.619</v>
@@ -821,43 +821,43 @@
         <v>24</v>
       </c>
       <c r="B3" t="n">
-        <v>45.04922087203472</v>
+        <v>4.971291092935664</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001286653185463499</v>
+        <v>0.07607434245889087</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3951780643310354</v>
+        <v>0.09054617213741735</v>
       </c>
       <c r="E3" t="n">
-        <v>10.80728710362606</v>
+        <v>2.256846780761196</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5682262357309322</v>
+        <v>0.04544411596283778</v>
       </c>
       <c r="G3" t="n">
-        <v>13.43112080548442</v>
+        <v>1.54882474708585</v>
       </c>
       <c r="H3" t="n">
-        <v>4.342115946016494</v>
+        <v>2.251486305885235</v>
       </c>
       <c r="I3" t="n">
-        <v>1.686419726322035</v>
+        <v>9.158881850512227</v>
       </c>
       <c r="J3" t="n">
-        <v>8.822167550120698</v>
+        <v>1.08702295401535</v>
       </c>
       <c r="K3" t="n">
-        <v>1.574063141705373</v>
+        <v>3.604829348118082</v>
       </c>
       <c r="L3" t="n">
-        <v>5.285891211370853</v>
+        <v>1.854363868379778</v>
       </c>
       <c r="M3" t="n">
-        <v>3.48116495450241</v>
+        <v>4.631080843681892</v>
       </c>
       <c r="N3" t="n">
-        <v>3.46804031621121</v>
+        <v>2.673995329902772</v>
       </c>
       <c r="O3" t="n">
         <v>104.65</v>
@@ -872,7 +872,7 @@
         <v>0.35</v>
       </c>
       <c r="S3" t="n">
-        <v>4.442089073875184</v>
+        <v>3.011950839395225</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -881,37 +881,37 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>2.693575513295827</v>
+        <v>15.54520354326996</v>
       </c>
       <c r="W3" t="n">
         <v>100000</v>
       </c>
       <c r="X3" t="n">
-        <v>9.296351168795328</v>
+        <v>15.11126222505268</v>
       </c>
       <c r="Y3" t="n">
-        <v>26.47545177181203</v>
+        <v>16.5964162713851</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.08040508961976217</v>
+        <v>0.3024940987422994</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.005357467343630261</v>
+        <v>0.00125822061786149</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.142487219857842</v>
+        <v>0.2819061063319032</v>
       </c>
       <c r="AC3" t="n">
         <v>0.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>44.30159130195483</v>
+        <v>19.78592468317675</v>
       </c>
       <c r="AE3" t="n">
         <v>0.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.6972420185991776</v>
+        <v>0.01775609416411895</v>
       </c>
       <c r="AG3" t="n">
         <v>48</v>
@@ -929,25 +929,25 @@
         <v>0.83</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.846995520367646</v>
+        <v>2.514037868745675</v>
       </c>
       <c r="AM3" t="n">
-        <v>4.848517750363304</v>
+        <v>2.460119409909252</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.235621567110113</v>
+        <v>1.20733782722826</v>
       </c>
       <c r="AP3" t="n">
-        <v>13.58280240821173</v>
+        <v>62.30111722183204</v>
       </c>
       <c r="AQ3" t="n">
         <v>15.31</v>
       </c>
       <c r="AR3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AS3" t="n">
         <v>0.11</v>
@@ -956,22 +956,22 @@
         <v>1.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.292913869596211</v>
+        <v>18.72283274695977</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.8958920692091406</v>
+        <v>14.48084791129498</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.8544794831849516</v>
+        <v>0.3757603948567754</v>
       </c>
       <c r="AX3" t="n">
-        <v>28.2582478586295</v>
+        <v>19.70998049773649</v>
       </c>
       <c r="AY3" t="n">
-        <v>27.78594531396306</v>
+        <v>102.93460023995</v>
       </c>
       <c r="AZ3" t="n">
-        <v>26.64566814131144</v>
+        <v>69.78960859478399</v>
       </c>
       <c r="BA3" t="n">
         <v>-1.619</v>
@@ -1021,43 +1021,43 @@
         <v>24</v>
       </c>
       <c r="B4" t="n">
-        <v>50.00262616023358</v>
+        <v>33.48904609485973</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001245660992740202</v>
+        <v>0.004891645686228227</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1984365798888209</v>
+        <v>0.09958005027402513</v>
       </c>
       <c r="E4" t="n">
-        <v>26.21515642147447</v>
+        <v>45.49838776957519</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01657908672985456</v>
+        <v>0.004252119617983219</v>
       </c>
       <c r="G4" t="n">
-        <v>3.856598946634203</v>
+        <v>7.437415542744149</v>
       </c>
       <c r="H4" t="n">
-        <v>5.112142031306155</v>
+        <v>6.642438108968728</v>
       </c>
       <c r="I4" t="n">
-        <v>3.208767030455561</v>
+        <v>1.31175391611329</v>
       </c>
       <c r="J4" t="n">
-        <v>5.787880465108706</v>
+        <v>1.952496934515305</v>
       </c>
       <c r="K4" t="n">
-        <v>3.92373378549914</v>
+        <v>1.372999035312285</v>
       </c>
       <c r="L4" t="n">
-        <v>2.498122189961463</v>
+        <v>6.502162610178068</v>
       </c>
       <c r="M4" t="n">
-        <v>4.744257564537151</v>
+        <v>3.926618850515009</v>
       </c>
       <c r="N4" t="n">
-        <v>6.071188897900377</v>
+        <v>1.482074875817333</v>
       </c>
       <c r="O4" t="n">
         <v>104.65</v>
@@ -1072,7 +1072,7 @@
         <v>0.35</v>
       </c>
       <c r="S4" t="n">
-        <v>2.431373394601861</v>
+        <v>5.244794338189208</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1081,37 +1081,37 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>13.27951153021614</v>
+        <v>14.6794060650535</v>
       </c>
       <c r="W4" t="n">
         <v>100000</v>
       </c>
       <c r="X4" t="n">
-        <v>44.29628520329605</v>
+        <v>3.016324609981023</v>
       </c>
       <c r="Y4" t="n">
-        <v>19.38674117984152</v>
+        <v>29.69157339204849</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.001560891039364982</v>
+        <v>0.3305422163031101</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.00156436732259925</v>
+        <v>0.001316569338748818</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.152367895537176</v>
+        <v>0.008489533723694678</v>
       </c>
       <c r="AC4" t="n">
         <v>0.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>32.00058177756998</v>
+        <v>49.87666181847085</v>
       </c>
       <c r="AE4" t="n">
         <v>0.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.004133904618453456</v>
+        <v>0.003542371683471929</v>
       </c>
       <c r="AG4" t="n">
         <v>48</v>
@@ -1129,25 +1129,25 @@
         <v>0.83</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.85870345265769</v>
+        <v>1.340783803263974</v>
       </c>
       <c r="AM4" t="n">
-        <v>7.288958305097344</v>
+        <v>1.277066226520884</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.17372771179297</v>
+        <v>1.590618772852654</v>
       </c>
       <c r="AP4" t="n">
-        <v>47.07271210100142</v>
+        <v>20.4170689735449</v>
       </c>
       <c r="AQ4" t="n">
         <v>15.31</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="AS4" t="n">
         <v>0.11</v>
@@ -1156,22 +1156,22 @@
         <v>1.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.075039968928851</v>
+        <v>8.679842392447782</v>
       </c>
       <c r="AV4" t="n">
-        <v>16.19252870179962</v>
+        <v>15.22972185403957</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.286821739198307</v>
+        <v>2.409566503645442</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.184776009685865</v>
+        <v>17.2665832778207</v>
       </c>
       <c r="AY4" t="n">
-        <v>119.2716740725615</v>
+        <v>24.8675918585849</v>
       </c>
       <c r="AZ4" t="n">
-        <v>10.07295764611962</v>
+        <v>58.39084446989466</v>
       </c>
       <c r="BA4" t="n">
         <v>-1.619</v>
@@ -1221,43 +1221,43 @@
         <v>24</v>
       </c>
       <c r="B5" t="n">
-        <v>11.50741283305824</v>
+        <v>1.581087775293525</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4869740651852533</v>
+        <v>0.8202444657982125</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1240747649619116</v>
+        <v>0.2811977891122274</v>
       </c>
       <c r="E5" t="n">
-        <v>47.35158347286297</v>
+        <v>21.02568338145344</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1080357628327504</v>
+        <v>0.06883997172219114</v>
       </c>
       <c r="G5" t="n">
-        <v>15.40347261241741</v>
+        <v>1.181911601034778</v>
       </c>
       <c r="H5" t="n">
-        <v>1.509532791638178</v>
+        <v>7.17545985340808</v>
       </c>
       <c r="I5" t="n">
-        <v>6.903647344527638</v>
+        <v>4.297272420348571</v>
       </c>
       <c r="J5" t="n">
-        <v>1.576482602348147</v>
+        <v>6.580737174009915</v>
       </c>
       <c r="K5" t="n">
-        <v>1.447729320244158</v>
+        <v>5.154043399366891</v>
       </c>
       <c r="L5" t="n">
-        <v>5.180899499147241</v>
+        <v>2.30236188992855</v>
       </c>
       <c r="M5" t="n">
-        <v>1.059200142845375</v>
+        <v>1.422122767133648</v>
       </c>
       <c r="N5" t="n">
-        <v>1.320108929615552</v>
+        <v>3.562909149791134</v>
       </c>
       <c r="O5" t="n">
         <v>104.65</v>
@@ -1272,7 +1272,7 @@
         <v>0.35</v>
       </c>
       <c r="S5" t="n">
-        <v>7.755980866833339</v>
+        <v>2.389960822886968</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1281,37 +1281,37 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.084665585635268</v>
+        <v>37.16848061560697</v>
       </c>
       <c r="W5" t="n">
         <v>100000</v>
       </c>
       <c r="X5" t="n">
-        <v>32.23290052455344</v>
+        <v>4.024521689156173</v>
       </c>
       <c r="Y5" t="n">
-        <v>41.12749845418892</v>
+        <v>31.64793098689891</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01503994394288836</v>
+        <v>0.3852513299316344</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03498851960935177</v>
+        <v>0.002284236269779356</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1179051755733009</v>
+        <v>0.1149547877069496</v>
       </c>
       <c r="AC5" t="n">
         <v>0.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>65.78219870818995</v>
+        <v>51.18643807908917</v>
       </c>
       <c r="AE5" t="n">
         <v>0.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.02240748412644234</v>
+        <v>0.5042798964731621</v>
       </c>
       <c r="AG5" t="n">
         <v>48</v>
@@ -1329,25 +1329,25 @@
         <v>0.83</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.582589727833123</v>
+        <v>1.155642967594846</v>
       </c>
       <c r="AM5" t="n">
-        <v>4.740005870076434</v>
+        <v>3.221713738384235</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.463494759406162</v>
+        <v>2.761569441441273</v>
       </c>
       <c r="AP5" t="n">
-        <v>43.3868641965389</v>
+        <v>50.61193620468695</v>
       </c>
       <c r="AQ5" t="n">
         <v>15.31</v>
       </c>
       <c r="AR5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AS5" t="n">
         <v>0.11</v>
@@ -1356,22 +1356,22 @@
         <v>1.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.65257904612483</v>
+        <v>9.670636484510828</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.8248072048121354</v>
+        <v>3.224384451764877</v>
       </c>
       <c r="AW5" t="n">
-        <v>16.08256523440952</v>
+        <v>13.49305669425157</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.410006598788049</v>
+        <v>40.67875335703212</v>
       </c>
       <c r="AY5" t="n">
-        <v>168.3204415884099</v>
+        <v>14.56276145561666</v>
       </c>
       <c r="AZ5" t="n">
-        <v>38.43906851077592</v>
+        <v>92.34145225680408</v>
       </c>
       <c r="BA5" t="n">
         <v>-1.619</v>
@@ -1421,49 +1421,49 @@
         <v>24</v>
       </c>
       <c r="B6" t="n">
-        <v>2.829343587487544</v>
+        <v>4.888610366019797</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3787314635263621</v>
+        <v>0.1415149742829915</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4423038944543806</v>
+        <v>0.1578817008148456</v>
       </c>
       <c r="E6" t="n">
-        <v>7.008015897647759</v>
+        <v>1.843310729143013</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07535476854921849</v>
+        <v>0.009973475029351923</v>
       </c>
       <c r="G6" t="n">
-        <v>1.512455292869509</v>
+        <v>11.44275918017049</v>
       </c>
       <c r="H6" t="n">
-        <v>4.309411509718792</v>
+        <v>3.871162524872898</v>
       </c>
       <c r="I6" t="n">
-        <v>9.201096627435533</v>
+        <v>2.561595557619472</v>
       </c>
       <c r="J6" t="n">
-        <v>9.809493222734494</v>
+        <v>3.044191078198895</v>
       </c>
       <c r="K6" t="n">
-        <v>1.360609267930378</v>
+        <v>2.200598401532612</v>
       </c>
       <c r="L6" t="n">
-        <v>1.903238049841896</v>
+        <v>2.382195378441131</v>
       </c>
       <c r="M6" t="n">
-        <v>9.396994755807995</v>
+        <v>1.145898719689626</v>
       </c>
       <c r="N6" t="n">
-        <v>5.96213214427007</v>
+        <v>2.566465580426303</v>
       </c>
       <c r="O6" t="n">
         <v>104.65</v>
       </c>
       <c r="P6" t="n">
-        <v>0.001</v>
+        <v>0.5</v>
       </c>
       <c r="Q6" t="n">
         <v>0.11</v>
@@ -1472,7 +1472,7 @@
         <v>0.35</v>
       </c>
       <c r="S6" t="n">
-        <v>1.843707798596227</v>
+        <v>5.097854997051264</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1481,37 +1481,37 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>14.79326025954465</v>
+        <v>6.471054061771331</v>
       </c>
       <c r="W6" t="n">
         <v>100000</v>
       </c>
       <c r="X6" t="n">
-        <v>37.22083125855505</v>
+        <v>1.28714901979857</v>
       </c>
       <c r="Y6" t="n">
-        <v>67.36364194017906</v>
+        <v>43.43821064726711</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3060462602867943</v>
+        <v>0.08035063802654865</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1204325960259179</v>
+        <v>0.00138600325531781</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.002023486927958422</v>
+        <v>0.01073869442407582</v>
       </c>
       <c r="AC6" t="n">
         <v>0.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>51.58964949127348</v>
+        <v>29.91327786118845</v>
       </c>
       <c r="AE6" t="n">
         <v>0.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.05272899656872081</v>
+        <v>0.08930053574997802</v>
       </c>
       <c r="AG6" t="n">
         <v>48</v>
@@ -1520,7 +1520,7 @@
         <v>30.46</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.001</v>
+        <v>0.5</v>
       </c>
       <c r="AJ6" t="n">
         <v>0.11</v>
@@ -1529,19 +1529,19 @@
         <v>0.83</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.333553335611746</v>
+        <v>1.76473151009333</v>
       </c>
       <c r="AM6" t="n">
-        <v>6.629578669539731</v>
+        <v>1.813933662741134</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>3.809392693311359</v>
+        <v>1.23338858071764</v>
       </c>
       <c r="AP6" t="n">
-        <v>18.23857009402648</v>
+        <v>47.60996137278767</v>
       </c>
       <c r="AQ6" t="n">
         <v>15.31</v>
@@ -1556,22 +1556,22 @@
         <v>1.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>99.12383587438974</v>
+        <v>80.1761860486875</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.727341452950008</v>
+        <v>5.76464243285404</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.578113566743263</v>
+        <v>19.55107077675466</v>
       </c>
       <c r="AX6" t="n">
-        <v>22.7149669454627</v>
+        <v>46.91659434986416</v>
       </c>
       <c r="AY6" t="n">
-        <v>114.3996284141377</v>
+        <v>266.8241790068947</v>
       </c>
       <c r="AZ6" t="n">
-        <v>124.5930200509358</v>
+        <v>25.80961963325334</v>
       </c>
       <c r="BA6" t="n">
         <v>-1.619</v>
@@ -1621,49 +1621,49 @@
         <v>24</v>
       </c>
       <c r="B7" t="n">
-        <v>2.498438864001307</v>
+        <v>15.52237759198443</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1022201747218028</v>
+        <v>0.2972669327137361</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0864318685545659</v>
+        <v>0.00827044741359213</v>
       </c>
       <c r="E7" t="n">
-        <v>38.7039746207796</v>
+        <v>8.722733926627253</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002076280932044313</v>
+        <v>0.001242573337617079</v>
       </c>
       <c r="G7" t="n">
-        <v>27.5108629254043</v>
+        <v>1.905434264712514</v>
       </c>
       <c r="H7" t="n">
-        <v>3.376401164271756</v>
+        <v>4.32466997504502</v>
       </c>
       <c r="I7" t="n">
-        <v>5.845350936667579</v>
+        <v>3.183752721197497</v>
       </c>
       <c r="J7" t="n">
-        <v>5.876593846814259</v>
+        <v>3.18621396446507</v>
       </c>
       <c r="K7" t="n">
-        <v>2.156591751754738</v>
+        <v>2.237054176787484</v>
       </c>
       <c r="L7" t="n">
-        <v>3.654215499373197</v>
+        <v>2.639741305892563</v>
       </c>
       <c r="M7" t="n">
-        <v>2.387364454026037</v>
+        <v>1.193681419538303</v>
       </c>
       <c r="N7" t="n">
-        <v>5.28998366286024</v>
+        <v>1.723597544672132</v>
       </c>
       <c r="O7" t="n">
         <v>104.65</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5</v>
+        <v>0.001</v>
       </c>
       <c r="Q7" t="n">
         <v>0.11</v>
@@ -1672,7 +1672,7 @@
         <v>0.35</v>
       </c>
       <c r="S7" t="n">
-        <v>7.962323061080076</v>
+        <v>7.354294285576749</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1681,37 +1681,37 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>2.145283825842406</v>
+        <v>81.32937145368405</v>
       </c>
       <c r="W7" t="n">
         <v>100000</v>
       </c>
       <c r="X7" t="n">
-        <v>5.801586900863168</v>
+        <v>1.547947750441182</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.99232617726826</v>
+        <v>60.98032327898827</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.8389600516710979</v>
+        <v>0.9881040607536045</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.006926162645822807</v>
+        <v>0.003625144850183372</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.005613513424428195</v>
+        <v>0.06135621432299354</v>
       </c>
       <c r="AC7" t="n">
         <v>0.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>48.84669773679011</v>
+        <v>56.49609365229158</v>
       </c>
       <c r="AE7" t="n">
         <v>0.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1272221346864865</v>
+        <v>0.004613560062095413</v>
       </c>
       <c r="AG7" t="n">
         <v>48</v>
@@ -1729,25 +1729,25 @@
         <v>0.83</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.62999151477756</v>
+        <v>1.017310324645986</v>
       </c>
       <c r="AM7" t="n">
-        <v>5.387415347845547</v>
+        <v>6.562191222184445</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>2.309041988619749</v>
+        <v>2.78314483999369</v>
       </c>
       <c r="AP7" t="n">
-        <v>10.69582965540827</v>
+        <v>13.64976756712682</v>
       </c>
       <c r="AQ7" t="n">
         <v>15.31</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AS7" t="n">
         <v>0.11</v>
@@ -1756,22 +1756,22 @@
         <v>1.3</v>
       </c>
       <c r="AU7" t="n">
-        <v>5.331750632089257</v>
+        <v>16.56819726099274</v>
       </c>
       <c r="AV7" t="n">
-        <v>56.50943011876728</v>
+        <v>1.414361399463934</v>
       </c>
       <c r="AW7" t="n">
-        <v>27.14004053390751</v>
+        <v>21.08528390173183</v>
       </c>
       <c r="AX7" t="n">
-        <v>104.1542035618586</v>
+        <v>33.87813692424081</v>
       </c>
       <c r="AY7" t="n">
-        <v>10.78750510597289</v>
+        <v>50.66509598618173</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.440259271381433</v>
+        <v>6.986518738909272</v>
       </c>
       <c r="BA7" t="n">
         <v>-1.619</v>
@@ -1821,49 +1821,49 @@
         <v>24</v>
       </c>
       <c r="B8" t="n">
-        <v>41.48390108192338</v>
+        <v>3.891390473722628</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2439236919555664</v>
+        <v>0.6716716360342583</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1262444790029573</v>
+        <v>0.1079905439051008</v>
       </c>
       <c r="E8" t="n">
-        <v>28.09839921488442</v>
+        <v>9.769024731983848</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004366256893307832</v>
+        <v>0.02045509118351847</v>
       </c>
       <c r="G8" t="n">
-        <v>8.29124589970453</v>
+        <v>14.3556729778797</v>
       </c>
       <c r="H8" t="n">
-        <v>6.014284752289801</v>
+        <v>2.922836652879346</v>
       </c>
       <c r="I8" t="n">
-        <v>3.545605291814265</v>
+        <v>2.296298607483519</v>
       </c>
       <c r="J8" t="n">
-        <v>1.113186736875172</v>
+        <v>1.205849378822387</v>
       </c>
       <c r="K8" t="n">
-        <v>6.927557116765813</v>
+        <v>9.174344157714399</v>
       </c>
       <c r="L8" t="n">
-        <v>3.868685125337972</v>
+        <v>8.454425024479606</v>
       </c>
       <c r="M8" t="n">
-        <v>1.387770156415798</v>
+        <v>1.066227687240824</v>
       </c>
       <c r="N8" t="n">
-        <v>8.747274081314082</v>
+        <v>3.561385075243187</v>
       </c>
       <c r="O8" t="n">
         <v>104.65</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001</v>
+        <v>0.5</v>
       </c>
       <c r="Q8" t="n">
         <v>0.11</v>
@@ -1872,7 +1872,7 @@
         <v>0.35</v>
       </c>
       <c r="S8" t="n">
-        <v>1.542139312918885</v>
+        <v>3.36333066081823</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1881,37 +1881,37 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>37.27752235253166</v>
+        <v>34.55494811029459</v>
       </c>
       <c r="W8" t="n">
         <v>100000</v>
       </c>
       <c r="X8" t="n">
-        <v>1.743150533910444</v>
+        <v>2.099218757024895</v>
       </c>
       <c r="Y8" t="n">
-        <v>52.58852848096944</v>
+        <v>46.91991146947734</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.2253289961738558</v>
+        <v>0.002003724429469213</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.02001240999917367</v>
+        <v>0.6227269486729339</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.8211126224620319</v>
+        <v>9.602009050054896</v>
       </c>
       <c r="AC8" t="n">
         <v>0.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>37.42414256951932</v>
+        <v>15.88464318862351</v>
       </c>
       <c r="AE8" t="n">
         <v>0.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.002612123465224618</v>
+        <v>0.006799625456914293</v>
       </c>
       <c r="AG8" t="n">
         <v>48</v>
@@ -1929,25 +1929,25 @@
         <v>0.83</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.146812533105363</v>
+        <v>2.69686282852086</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.397773235010427</v>
+        <v>1.111074983401099</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.243004898013252</v>
+        <v>1.925640031852098</v>
       </c>
       <c r="AP8" t="n">
-        <v>16.47186788984868</v>
+        <v>17.2737717698118</v>
       </c>
       <c r="AQ8" t="n">
         <v>15.31</v>
       </c>
       <c r="AR8" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AS8" t="n">
         <v>0.11</v>
@@ -1956,22 +1956,22 @@
         <v>1.3</v>
       </c>
       <c r="AU8" t="n">
-        <v>11.42157310539206</v>
+        <v>2.966193983677215</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.006378314526959</v>
+        <v>13.29920564540239</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.470866764979149</v>
+        <v>3.075079537681249</v>
       </c>
       <c r="AX8" t="n">
-        <v>174.3171826789804</v>
+        <v>7.494505284708182</v>
       </c>
       <c r="AY8" t="n">
-        <v>39.35520300284144</v>
+        <v>5.785103611199904</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.305697574043565</v>
+        <v>7.870767992679159</v>
       </c>
       <c r="BA8" t="n">
         <v>-1.619</v>
@@ -2021,43 +2021,43 @@
         <v>24</v>
       </c>
       <c r="B9" t="n">
-        <v>9.981429503733487</v>
+        <v>1.163380875592019</v>
       </c>
       <c r="C9" t="n">
-        <v>0.05184836713579528</v>
+        <v>0.4141073380012303</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4312160453495719</v>
+        <v>0.2593339355114364</v>
       </c>
       <c r="E9" t="n">
-        <v>2.664394762976626</v>
+        <v>3.860252830272614</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002452251364108389</v>
+        <v>0.003146653466208297</v>
       </c>
       <c r="G9" t="n">
-        <v>2.249017224907403</v>
+        <v>24.95859443069013</v>
       </c>
       <c r="H9" t="n">
-        <v>2.586023132425172</v>
+        <v>8.219739394194752</v>
       </c>
       <c r="I9" t="n">
-        <v>7.269281615712195</v>
+        <v>5.056312681697569</v>
       </c>
       <c r="J9" t="n">
-        <v>1.231899099741847</v>
+        <v>6.050992622435839</v>
       </c>
       <c r="K9" t="n">
-        <v>2.633368710208515</v>
+        <v>1.727709495838081</v>
       </c>
       <c r="L9" t="n">
-        <v>1.207691727631449</v>
+        <v>8.73793282208139</v>
       </c>
       <c r="M9" t="n">
-        <v>6.424315897375428</v>
+        <v>6.239834418425214</v>
       </c>
       <c r="N9" t="n">
-        <v>8.114211336916542</v>
+        <v>1.427529504941323</v>
       </c>
       <c r="O9" t="n">
         <v>104.65</v>
@@ -2072,7 +2072,7 @@
         <v>0.35</v>
       </c>
       <c r="S9" t="n">
-        <v>3.102374357083628</v>
+        <v>2.266908987874961</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -2081,37 +2081,37 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>17.22957619006512</v>
+        <v>92.05349986840952</v>
       </c>
       <c r="W9" t="n">
         <v>100000</v>
       </c>
       <c r="X9" t="n">
-        <v>44.61002808904887</v>
+        <v>1.817403411264175</v>
       </c>
       <c r="Y9" t="n">
-        <v>67.77411965499547</v>
+        <v>44.83578146439995</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.6544342349972997</v>
+        <v>0.03235250980867351</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03679323955920445</v>
+        <v>0.04394052556724366</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03488230114051698</v>
+        <v>6.529869036861911</v>
       </c>
       <c r="AC9" t="n">
         <v>0.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>60.72213745083901</v>
+        <v>10.94937500981717</v>
       </c>
       <c r="AE9" t="n">
         <v>0.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.004678697421120776</v>
+        <v>0.4231027250053204</v>
       </c>
       <c r="AG9" t="n">
         <v>48</v>
@@ -2129,25 +2129,25 @@
         <v>0.83</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.29160955616186</v>
+        <v>1.530523266700627</v>
       </c>
       <c r="AM9" t="n">
-        <v>3.623492095633401</v>
+        <v>2.346846678586495</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>3.376417847574152</v>
+        <v>1.780991301853134</v>
       </c>
       <c r="AP9" t="n">
-        <v>28.30766317513977</v>
+        <v>64.55316720527924</v>
       </c>
       <c r="AQ9" t="n">
         <v>15.31</v>
       </c>
       <c r="AR9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS9" t="n">
         <v>0.11</v>
@@ -2156,22 +2156,22 @@
         <v>1.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.488166817284831</v>
+        <v>39.91145576246209</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.157518679948051</v>
+        <v>13.3900038069803</v>
       </c>
       <c r="AW9" t="n">
-        <v>13.3388292178224</v>
+        <v>3.714751389534066</v>
       </c>
       <c r="AX9" t="n">
-        <v>30.98862847849199</v>
+        <v>22.83464619162016</v>
       </c>
       <c r="AY9" t="n">
-        <v>29.55999683758345</v>
+        <v>69.27978413956187</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.692002355797194</v>
+        <v>1.665493820634949</v>
       </c>
       <c r="BA9" t="n">
         <v>-1.619</v>
@@ -2221,43 +2221,43 @@
         <v>24</v>
       </c>
       <c r="B10" t="n">
-        <v>4.698165477742938</v>
+        <v>24.31119981011818</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3003780328067443</v>
+        <v>0.006731893234896454</v>
       </c>
       <c r="D10" t="n">
-        <v>0.06767238810819121</v>
+        <v>0.1830144079342389</v>
       </c>
       <c r="E10" t="n">
-        <v>9.593016706588287</v>
+        <v>19.3580463631489</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9747131866917508</v>
+        <v>0.07468661015877416</v>
       </c>
       <c r="G10" t="n">
-        <v>2.145381235137885</v>
+        <v>40.24026800617218</v>
       </c>
       <c r="H10" t="n">
-        <v>1.982816946866819</v>
+        <v>4.188948709632963</v>
       </c>
       <c r="I10" t="n">
-        <v>2.219919329807045</v>
+        <v>2.467770020991745</v>
       </c>
       <c r="J10" t="n">
-        <v>2.316987994080995</v>
+        <v>2.568523307301584</v>
       </c>
       <c r="K10" t="n">
-        <v>4.94825880471943</v>
+        <v>2.206321970785715</v>
       </c>
       <c r="L10" t="n">
-        <v>5.304512308187486</v>
+        <v>4.59338086443397</v>
       </c>
       <c r="M10" t="n">
-        <v>4.947739548280642</v>
+        <v>4.066584357227869</v>
       </c>
       <c r="N10" t="n">
-        <v>3.297913929801099</v>
+        <v>2.487332855731655</v>
       </c>
       <c r="O10" t="n">
         <v>104.65</v>
@@ -2272,7 +2272,7 @@
         <v>0.35</v>
       </c>
       <c r="S10" t="n">
-        <v>9.955524658247052</v>
+        <v>4.764761073110518</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -2281,37 +2281,37 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>4.035218653549185</v>
+        <v>10.47149656453435</v>
       </c>
       <c r="W10" t="n">
         <v>100000</v>
       </c>
       <c r="X10" t="n">
-        <v>2.812595216999397</v>
+        <v>5.323234114832539</v>
       </c>
       <c r="Y10" t="n">
-        <v>39.22034397338348</v>
+        <v>62.01364687243713</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.1515229604478157</v>
+        <v>0.4381791017788009</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.02973145326879196</v>
+        <v>0.01669598207757709</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.255481030159606</v>
+        <v>7.793105812279869</v>
       </c>
       <c r="AC10" t="n">
         <v>0.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>36.84910710354424</v>
+        <v>45.58623248092</v>
       </c>
       <c r="AE10" t="n">
         <v>0.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.3518357539448436</v>
+        <v>0.00764295573575936</v>
       </c>
       <c r="AG10" t="n">
         <v>48</v>
@@ -2320,7 +2320,7 @@
         <v>30.46</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.5</v>
+        <v>0.001</v>
       </c>
       <c r="AJ10" t="n">
         <v>0.11</v>
@@ -2329,25 +2329,25 @@
         <v>0.83</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.79888069090897</v>
+        <v>3.086305859442327</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.077288158218722</v>
+        <v>1.821176368429866</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>2.01426259443009</v>
+        <v>1.389892626672453</v>
       </c>
       <c r="AP10" t="n">
-        <v>20.57583258657502</v>
+        <v>61.66876989842974</v>
       </c>
       <c r="AQ10" t="n">
         <v>15.31</v>
       </c>
       <c r="AR10" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="AS10" t="n">
         <v>0.11</v>
@@ -2356,22 +2356,22 @@
         <v>1.3</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.183811271949442</v>
+        <v>75.37920174282334</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.472610538054062</v>
+        <v>1.382214011154605</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.93929661713945</v>
+        <v>16.10656023809455</v>
       </c>
       <c r="AX10" t="n">
-        <v>22.23388496063458</v>
+        <v>12.06675773247844</v>
       </c>
       <c r="AY10" t="n">
-        <v>19.85242697621881</v>
+        <v>211.7111147922239</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.283722857815571</v>
+        <v>57.40698583073245</v>
       </c>
       <c r="BA10" t="n">
         <v>-1.619</v>

--- a/input_home.xlsx
+++ b/input_home.xlsx
@@ -421,49 +421,49 @@
         <v>24</v>
       </c>
       <c r="B1" t="n">
-        <v>21.08280781737069</v>
+        <v>2.943904845837354</v>
       </c>
       <c r="C1" t="n">
-        <v>0.09138178310500439</v>
+        <v>0.1320166740049059</v>
       </c>
       <c r="D1" t="n">
-        <v>0.3402716441383726</v>
+        <v>0.2378175488335919</v>
       </c>
       <c r="E1" t="n">
-        <v>1.483605087826981</v>
+        <v>40.64381977183632</v>
       </c>
       <c r="F1" t="n">
-        <v>0.02634415766252343</v>
+        <v>0.005858456936452504</v>
       </c>
       <c r="G1" t="n">
-        <v>24.01750891658013</v>
+        <v>14.81476628787477</v>
       </c>
       <c r="H1" t="n">
-        <v>3.680181500975511</v>
+        <v>7.445203188125006</v>
       </c>
       <c r="I1" t="n">
-        <v>2.108450680760779</v>
+        <v>2.171446286751072</v>
       </c>
       <c r="J1" t="n">
-        <v>3.089077785617069</v>
+        <v>1.212961188379789</v>
       </c>
       <c r="K1" t="n">
-        <v>2.826370154346388</v>
+        <v>2.489387166398308</v>
       </c>
       <c r="L1" t="n">
-        <v>1.704695450324314</v>
+        <v>1.406800562583266</v>
       </c>
       <c r="M1" t="n">
-        <v>3.026294427652643</v>
+        <v>1.532383433117765</v>
       </c>
       <c r="N1" t="n">
-        <v>3.2225562496091</v>
+        <v>3.542825378100075</v>
       </c>
       <c r="O1" t="n">
         <v>104.65</v>
       </c>
       <c r="P1" t="n">
-        <v>0.5</v>
+        <v>0.001</v>
       </c>
       <c r="Q1" t="n">
         <v>0.11</v>
@@ -472,7 +472,7 @@
         <v>0.35</v>
       </c>
       <c r="S1" t="n">
-        <v>5.270588844336339</v>
+        <v>6.161029899050782</v>
       </c>
       <c r="T1" t="n">
         <v>0</v>
@@ -481,37 +481,37 @@
         <v>0</v>
       </c>
       <c r="V1" t="n">
-        <v>83.10452360132291</v>
+        <v>3.38180922452547</v>
       </c>
       <c r="W1" t="n">
         <v>100000</v>
       </c>
       <c r="X1" t="n">
-        <v>2.244385906775219</v>
+        <v>3.209510985018255</v>
       </c>
       <c r="Y1" t="n">
-        <v>61.60458904900389</v>
+        <v>21.95939999732665</v>
       </c>
       <c r="Z1" t="n">
-        <v>0.04500534761979962</v>
+        <v>0.7599832863063696</v>
       </c>
       <c r="AA1" t="n">
-        <v>0.3616321008050632</v>
+        <v>0.001497755027516798</v>
       </c>
       <c r="AB1" t="n">
-        <v>0.1007899881956241</v>
+        <v>0.8232903580892653</v>
       </c>
       <c r="AC1" t="n">
         <v>0.7</v>
       </c>
       <c r="AD1" t="n">
-        <v>42.48556516645564</v>
+        <v>66.55556543467802</v>
       </c>
       <c r="AE1" t="n">
         <v>0.5</v>
       </c>
       <c r="AF1" t="n">
-        <v>0.002154587783119306</v>
+        <v>0.005025751717722436</v>
       </c>
       <c r="AG1" t="n">
         <v>48</v>
@@ -529,25 +529,25 @@
         <v>0.83</v>
       </c>
       <c r="AL1" t="n">
-        <v>4.18297707285801</v>
+        <v>1.987672065994478</v>
       </c>
       <c r="AM1" t="n">
-        <v>1.623169339276551</v>
+        <v>1.818527690703367</v>
       </c>
       <c r="AN1" t="n">
         <v>0</v>
       </c>
       <c r="AO1" t="n">
-        <v>2.74689479944312</v>
+        <v>1.943034308322463</v>
       </c>
       <c r="AP1" t="n">
-        <v>19.26936572477398</v>
+        <v>21.1919729443492</v>
       </c>
       <c r="AQ1" t="n">
         <v>15.31</v>
       </c>
       <c r="AR1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AS1" t="n">
         <v>0.11</v>
@@ -556,22 +556,22 @@
         <v>1.3</v>
       </c>
       <c r="AU1" t="n">
-        <v>96.71368604447255</v>
+        <v>15.97092837607913</v>
       </c>
       <c r="AV1" t="n">
-        <v>1.632988112504921</v>
+        <v>4.870803405876305</v>
       </c>
       <c r="AW1" t="n">
-        <v>0.3800239630148674</v>
+        <v>2.949691680154227</v>
       </c>
       <c r="AX1" t="n">
-        <v>88.65705935882808</v>
+        <v>68.31565217494659</v>
       </c>
       <c r="AY1" t="n">
-        <v>20.62588145825003</v>
+        <v>39.95576900442013</v>
       </c>
       <c r="AZ1" t="n">
-        <v>62.82354858990544</v>
+        <v>46.40372956311876</v>
       </c>
       <c r="BA1" t="n">
         <v>-1.619</v>
@@ -621,49 +621,49 @@
         <v>24</v>
       </c>
       <c r="B2" t="n">
-        <v>2.052317625358281</v>
+        <v>1.142256905167602</v>
       </c>
       <c r="C2" t="n">
-        <v>0.03321714991009268</v>
+        <v>0.02288223486079671</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4238354188208024</v>
+        <v>0.4388365399695799</v>
       </c>
       <c r="E2" t="n">
-        <v>16.39121620536209</v>
+        <v>6.451960485743949</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03330015943360494</v>
+        <v>0.0377844969754654</v>
       </c>
       <c r="G2" t="n">
-        <v>1.354295336361108</v>
+        <v>35.8311856616878</v>
       </c>
       <c r="H2" t="n">
-        <v>5.980665894838839</v>
+        <v>7.038786547511382</v>
       </c>
       <c r="I2" t="n">
-        <v>1.302306694914315</v>
+        <v>2.643049283352905</v>
       </c>
       <c r="J2" t="n">
-        <v>6.531469336173868</v>
+        <v>3.530313408694075</v>
       </c>
       <c r="K2" t="n">
-        <v>3.970840513339755</v>
+        <v>5.709058591007432</v>
       </c>
       <c r="L2" t="n">
-        <v>3.25816580916512</v>
+        <v>1.610936694155367</v>
       </c>
       <c r="M2" t="n">
-        <v>1.94743993814401</v>
+        <v>1.394520225031062</v>
       </c>
       <c r="N2" t="n">
-        <v>3.540738210468991</v>
+        <v>7.433156164309776</v>
       </c>
       <c r="O2" t="n">
         <v>104.65</v>
       </c>
       <c r="P2" t="n">
-        <v>0.001</v>
+        <v>0.5</v>
       </c>
       <c r="Q2" t="n">
         <v>0.11</v>
@@ -672,7 +672,7 @@
         <v>0.35</v>
       </c>
       <c r="S2" t="n">
-        <v>3.311129326132998</v>
+        <v>6.223488741818016</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -681,37 +681,37 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>6.319459761491423</v>
+        <v>38.89991481492034</v>
       </c>
       <c r="W2" t="n">
         <v>100000</v>
       </c>
       <c r="X2" t="n">
-        <v>29.95387502568423</v>
+        <v>7.342219151908855</v>
       </c>
       <c r="Y2" t="n">
-        <v>54.76083510852956</v>
+        <v>44.97718026202978</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01249250912443576</v>
+        <v>0.00209326660995892</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2742024247088334</v>
+        <v>0.001023040905166854</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.304008036011061</v>
+        <v>0.002148287160276235</v>
       </c>
       <c r="AC2" t="n">
         <v>0.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>25.7878795684578</v>
+        <v>61.6652424033637</v>
       </c>
       <c r="AE2" t="n">
         <v>0.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0268053459161071</v>
+        <v>0.6774535532991047</v>
       </c>
       <c r="AG2" t="n">
         <v>48</v>
@@ -729,25 +729,25 @@
         <v>0.83</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.032505122652547</v>
+        <v>2.133950003225624</v>
       </c>
       <c r="AM2" t="n">
-        <v>5.134626703865262</v>
+        <v>3.026709356433095</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.605261181572286</v>
+        <v>1.090769859581709</v>
       </c>
       <c r="AP2" t="n">
-        <v>66.1738680371611</v>
+        <v>40.41040139667451</v>
       </c>
       <c r="AQ2" t="n">
         <v>15.31</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="AS2" t="n">
         <v>0.11</v>
@@ -756,22 +756,22 @@
         <v>1.3</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.995346633609642</v>
+        <v>7.239383984316127</v>
       </c>
       <c r="AV2" t="n">
-        <v>64.49842282834626</v>
+        <v>6.576456836514687</v>
       </c>
       <c r="AW2" t="n">
-        <v>24.40251436869462</v>
+        <v>21.15397261684662</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.582352426946448</v>
+        <v>3.266000084162211</v>
       </c>
       <c r="AY2" t="n">
-        <v>48.4435297991561</v>
+        <v>37.1376409981337</v>
       </c>
       <c r="AZ2" t="n">
-        <v>10.92483256991497</v>
+        <v>61.71483422764106</v>
       </c>
       <c r="BA2" t="n">
         <v>-1.619</v>
@@ -821,43 +821,43 @@
         <v>24</v>
       </c>
       <c r="B3" t="n">
-        <v>4.971291092935664</v>
+        <v>62.93322113591307</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07607434245889087</v>
+        <v>0.5875589164344576</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09054617213741735</v>
+        <v>0.1192517203601987</v>
       </c>
       <c r="E3" t="n">
-        <v>2.256846780761196</v>
+        <v>18.85194524854172</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04544411596283778</v>
+        <v>0.4780449618851367</v>
       </c>
       <c r="G3" t="n">
-        <v>1.54882474708585</v>
+        <v>4.422572841282323</v>
       </c>
       <c r="H3" t="n">
-        <v>2.251486305885235</v>
+        <v>2.957957128624666</v>
       </c>
       <c r="I3" t="n">
-        <v>9.158881850512227</v>
+        <v>9.695207520135462</v>
       </c>
       <c r="J3" t="n">
-        <v>1.08702295401535</v>
+        <v>4.035233870768248</v>
       </c>
       <c r="K3" t="n">
-        <v>3.604829348118082</v>
+        <v>1.254185485333067</v>
       </c>
       <c r="L3" t="n">
-        <v>1.854363868379778</v>
+        <v>5.517825738846233</v>
       </c>
       <c r="M3" t="n">
-        <v>4.631080843681892</v>
+        <v>2.806803355760506</v>
       </c>
       <c r="N3" t="n">
-        <v>2.673995329902772</v>
+        <v>6.746095198404866</v>
       </c>
       <c r="O3" t="n">
         <v>104.65</v>
@@ -872,7 +872,7 @@
         <v>0.35</v>
       </c>
       <c r="S3" t="n">
-        <v>3.011950839395225</v>
+        <v>7.817863377536542</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -881,37 +881,37 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>15.54520354326996</v>
+        <v>4.539475841604171</v>
       </c>
       <c r="W3" t="n">
         <v>100000</v>
       </c>
       <c r="X3" t="n">
-        <v>15.11126222505268</v>
+        <v>1.459537707170697</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.5964162713851</v>
+        <v>64.9379516434237</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3024940987422994</v>
+        <v>0.01406932410860022</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.00125822061786149</v>
+        <v>0.02965800951069102</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2819061063319032</v>
+        <v>0.002354231390144216</v>
       </c>
       <c r="AC3" t="n">
         <v>0.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>19.78592468317675</v>
+        <v>33.8076603478586</v>
       </c>
       <c r="AE3" t="n">
         <v>0.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.01775609416411895</v>
+        <v>0.7938740342562757</v>
       </c>
       <c r="AG3" t="n">
         <v>48</v>
@@ -929,25 +929,25 @@
         <v>0.83</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.514037868745675</v>
+        <v>6.280321171855211</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.460119409909252</v>
+        <v>4.518545104990062</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.20733782722826</v>
+        <v>3.189764567188345</v>
       </c>
       <c r="AP3" t="n">
-        <v>62.30111722183204</v>
+        <v>16.94668961545493</v>
       </c>
       <c r="AQ3" t="n">
         <v>15.31</v>
       </c>
       <c r="AR3" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="AS3" t="n">
         <v>0.11</v>
@@ -956,22 +956,22 @@
         <v>1.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>18.72283274695977</v>
+        <v>12.66691452820016</v>
       </c>
       <c r="AV3" t="n">
-        <v>14.48084791129498</v>
+        <v>18.08295038794937</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.3757603948567754</v>
+        <v>4.660632048342896</v>
       </c>
       <c r="AX3" t="n">
-        <v>19.70998049773649</v>
+        <v>3.595279075608639</v>
       </c>
       <c r="AY3" t="n">
-        <v>102.93460023995</v>
+        <v>185.8328106414996</v>
       </c>
       <c r="AZ3" t="n">
-        <v>69.78960859478399</v>
+        <v>5.510226910953176</v>
       </c>
       <c r="BA3" t="n">
         <v>-1.619</v>
@@ -1021,43 +1021,43 @@
         <v>24</v>
       </c>
       <c r="B4" t="n">
-        <v>33.48904609485973</v>
+        <v>18.66751147693502</v>
       </c>
       <c r="C4" t="n">
-        <v>0.004891645686228227</v>
+        <v>0.03905724850565502</v>
       </c>
       <c r="D4" t="n">
-        <v>0.09958005027402513</v>
+        <v>0.04170528823976088</v>
       </c>
       <c r="E4" t="n">
-        <v>45.49838776957519</v>
+        <v>6.283445451947586</v>
       </c>
       <c r="F4" t="n">
-        <v>0.004252119617983219</v>
+        <v>0.009431168351953869</v>
       </c>
       <c r="G4" t="n">
-        <v>7.437415542744149</v>
+        <v>11.92501011921299</v>
       </c>
       <c r="H4" t="n">
-        <v>6.642438108968728</v>
+        <v>9.206106465185988</v>
       </c>
       <c r="I4" t="n">
-        <v>1.31175391611329</v>
+        <v>3.203669001203268</v>
       </c>
       <c r="J4" t="n">
-        <v>1.952496934515305</v>
+        <v>3.145144581488121</v>
       </c>
       <c r="K4" t="n">
-        <v>1.372999035312285</v>
+        <v>1.941346833538909</v>
       </c>
       <c r="L4" t="n">
-        <v>6.502162610178068</v>
+        <v>5.175664013966968</v>
       </c>
       <c r="M4" t="n">
-        <v>3.926618850515009</v>
+        <v>1.135059463322174</v>
       </c>
       <c r="N4" t="n">
-        <v>1.482074875817333</v>
+        <v>1.259363891389082</v>
       </c>
       <c r="O4" t="n">
         <v>104.65</v>
@@ -1072,7 +1072,7 @@
         <v>0.35</v>
       </c>
       <c r="S4" t="n">
-        <v>5.244794338189208</v>
+        <v>4.66687863644488</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1081,37 +1081,37 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>14.6794060650535</v>
+        <v>12.16122962048619</v>
       </c>
       <c r="W4" t="n">
         <v>100000</v>
       </c>
       <c r="X4" t="n">
-        <v>3.016324609981023</v>
+        <v>2.723471953111264</v>
       </c>
       <c r="Y4" t="n">
-        <v>29.69157339204849</v>
+        <v>62.99550159586146</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.3305422163031101</v>
+        <v>0.2028530322789298</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.001316569338748818</v>
+        <v>0.01604481768259427</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.008489533723694678</v>
+        <v>3.478985018805266</v>
       </c>
       <c r="AC4" t="n">
         <v>0.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>49.87666181847085</v>
+        <v>43.82291832486179</v>
       </c>
       <c r="AE4" t="n">
         <v>0.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.003542371683471929</v>
+        <v>0.007957615079758871</v>
       </c>
       <c r="AG4" t="n">
         <v>48</v>
@@ -1129,25 +1129,25 @@
         <v>0.83</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.340783803263974</v>
+        <v>1.101171084267062</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.277066226520884</v>
+        <v>5.137123099285963</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.590618772852654</v>
+        <v>1.652095380889643</v>
       </c>
       <c r="AP4" t="n">
-        <v>20.4170689735449</v>
+        <v>46.38939760204592</v>
       </c>
       <c r="AQ4" t="n">
         <v>15.31</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="AS4" t="n">
         <v>0.11</v>
@@ -1156,22 +1156,22 @@
         <v>1.3</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.679842392447782</v>
+        <v>9.126067472255629</v>
       </c>
       <c r="AV4" t="n">
-        <v>15.22972185403957</v>
+        <v>1.379523807542082</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.409566503645442</v>
+        <v>2.26414260967574</v>
       </c>
       <c r="AX4" t="n">
-        <v>17.2665832778207</v>
+        <v>4.085595739433664</v>
       </c>
       <c r="AY4" t="n">
-        <v>24.8675918585849</v>
+        <v>15.59444777634635</v>
       </c>
       <c r="AZ4" t="n">
-        <v>58.39084446989466</v>
+        <v>18.68307440583455</v>
       </c>
       <c r="BA4" t="n">
         <v>-1.619</v>
@@ -1221,43 +1221,43 @@
         <v>24</v>
       </c>
       <c r="B5" t="n">
-        <v>1.581087775293525</v>
+        <v>2.580542317524676</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8202444657982125</v>
+        <v>0.03701863267612374</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2811977891122274</v>
+        <v>0.248812929501718</v>
       </c>
       <c r="E5" t="n">
-        <v>21.02568338145344</v>
+        <v>10.0237552576225</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06883997172219114</v>
+        <v>0.09083492029079764</v>
       </c>
       <c r="G5" t="n">
-        <v>1.181911601034778</v>
+        <v>9.438497492849629</v>
       </c>
       <c r="H5" t="n">
-        <v>7.17545985340808</v>
+        <v>7.480145959447963</v>
       </c>
       <c r="I5" t="n">
-        <v>4.297272420348571</v>
+        <v>3.971823249574616</v>
       </c>
       <c r="J5" t="n">
-        <v>6.580737174009915</v>
+        <v>1.530325937870196</v>
       </c>
       <c r="K5" t="n">
-        <v>5.154043399366891</v>
+        <v>6.573639624576724</v>
       </c>
       <c r="L5" t="n">
-        <v>2.30236188992855</v>
+        <v>2.637926749535464</v>
       </c>
       <c r="M5" t="n">
-        <v>1.422122767133648</v>
+        <v>2.082500031926424</v>
       </c>
       <c r="N5" t="n">
-        <v>3.562909149791134</v>
+        <v>8.740250345201904</v>
       </c>
       <c r="O5" t="n">
         <v>104.65</v>
@@ -1272,7 +1272,7 @@
         <v>0.35</v>
       </c>
       <c r="S5" t="n">
-        <v>2.389960822886968</v>
+        <v>5.496124764571769</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1281,37 +1281,37 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>37.16848061560697</v>
+        <v>3.588060711769225</v>
       </c>
       <c r="W5" t="n">
         <v>100000</v>
       </c>
       <c r="X5" t="n">
-        <v>4.024521689156173</v>
+        <v>5.251442133847002</v>
       </c>
       <c r="Y5" t="n">
-        <v>31.64793098689891</v>
+        <v>43.69790708086976</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.3852513299316344</v>
+        <v>0.0472643849355594</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.002284236269779356</v>
+        <v>0.01492600701444821</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1149547877069496</v>
+        <v>0.007438980394916481</v>
       </c>
       <c r="AC5" t="n">
         <v>0.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>51.18643807908917</v>
+        <v>12.66144376175419</v>
       </c>
       <c r="AE5" t="n">
         <v>0.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.5042798964731621</v>
+        <v>0.005506471382752459</v>
       </c>
       <c r="AG5" t="n">
         <v>48</v>
@@ -1329,19 +1329,19 @@
         <v>0.83</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.155642967594846</v>
+        <v>7.133618215619662</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.221713738384235</v>
+        <v>2.715573356850005</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>2.761569441441273</v>
+        <v>2.919336959257504</v>
       </c>
       <c r="AP5" t="n">
-        <v>50.61193620468695</v>
+        <v>32.25089575203523</v>
       </c>
       <c r="AQ5" t="n">
         <v>15.31</v>
@@ -1356,22 +1356,22 @@
         <v>1.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>9.670636484510828</v>
+        <v>76.17396311332023</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.224384451764877</v>
+        <v>3.993029498321309</v>
       </c>
       <c r="AW5" t="n">
-        <v>13.49305669425157</v>
+        <v>1.501430137052102</v>
       </c>
       <c r="AX5" t="n">
-        <v>40.67875335703212</v>
+        <v>4.952470931928417</v>
       </c>
       <c r="AY5" t="n">
-        <v>14.56276145561666</v>
+        <v>4.906511554701446</v>
       </c>
       <c r="AZ5" t="n">
-        <v>92.34145225680408</v>
+        <v>1.846242595881013</v>
       </c>
       <c r="BA5" t="n">
         <v>-1.619</v>
@@ -1421,49 +1421,49 @@
         <v>24</v>
       </c>
       <c r="B6" t="n">
-        <v>4.888610366019797</v>
+        <v>4.199595565510112</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1415149742829915</v>
+        <v>0.01354432848739687</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1578817008148456</v>
+        <v>0.1808979579455869</v>
       </c>
       <c r="E6" t="n">
-        <v>1.843310729143013</v>
+        <v>9.205067139979217</v>
       </c>
       <c r="F6" t="n">
-        <v>0.009973475029351923</v>
+        <v>0.2681032920401046</v>
       </c>
       <c r="G6" t="n">
-        <v>11.44275918017049</v>
+        <v>24.23656771113908</v>
       </c>
       <c r="H6" t="n">
-        <v>3.871162524872898</v>
+        <v>4.368293974772855</v>
       </c>
       <c r="I6" t="n">
-        <v>2.561595557619472</v>
+        <v>2.838532830156915</v>
       </c>
       <c r="J6" t="n">
-        <v>3.044191078198895</v>
+        <v>2.92759367030293</v>
       </c>
       <c r="K6" t="n">
-        <v>2.200598401532612</v>
+        <v>2.279812413870409</v>
       </c>
       <c r="L6" t="n">
-        <v>2.382195378441131</v>
+        <v>2.263676736485337</v>
       </c>
       <c r="M6" t="n">
-        <v>1.145898719689626</v>
+        <v>1.957459906388983</v>
       </c>
       <c r="N6" t="n">
-        <v>2.566465580426303</v>
+        <v>2.839945868144257</v>
       </c>
       <c r="O6" t="n">
         <v>104.65</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5</v>
+        <v>0.001</v>
       </c>
       <c r="Q6" t="n">
         <v>0.11</v>
@@ -1472,7 +1472,7 @@
         <v>0.35</v>
       </c>
       <c r="S6" t="n">
-        <v>5.097854997051264</v>
+        <v>2.728482158519362</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1481,37 +1481,37 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>6.471054061771331</v>
+        <v>1.987772830683544</v>
       </c>
       <c r="W6" t="n">
         <v>100000</v>
       </c>
       <c r="X6" t="n">
-        <v>1.28714901979857</v>
+        <v>61.0917233634554</v>
       </c>
       <c r="Y6" t="n">
-        <v>43.43821064726711</v>
+        <v>31.16826176769256</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.08035063802654865</v>
+        <v>0.3155838350453041</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.00138600325531781</v>
+        <v>0.00509781385199636</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.01073869442407582</v>
+        <v>4.070896548329432</v>
       </c>
       <c r="AC6" t="n">
         <v>0.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>29.91327786118845</v>
+        <v>55.72003564873072</v>
       </c>
       <c r="AE6" t="n">
         <v>0.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.08930053574997802</v>
+        <v>0.6230317154119196</v>
       </c>
       <c r="AG6" t="n">
         <v>48</v>
@@ -1529,25 +1529,25 @@
         <v>0.83</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.76473151009333</v>
+        <v>1.56289288222457</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.813933662741134</v>
+        <v>1.698882545433575</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>1.23338858071764</v>
+        <v>2.341107927356732</v>
       </c>
       <c r="AP6" t="n">
-        <v>47.60996137278767</v>
+        <v>17.97030418734511</v>
       </c>
       <c r="AQ6" t="n">
         <v>15.31</v>
       </c>
       <c r="AR6" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="AS6" t="n">
         <v>0.11</v>
@@ -1556,22 +1556,22 @@
         <v>1.3</v>
       </c>
       <c r="AU6" t="n">
-        <v>80.1761860486875</v>
+        <v>1.427419217272208</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.76464243285404</v>
+        <v>2.821999310861725</v>
       </c>
       <c r="AW6" t="n">
-        <v>19.55107077675466</v>
+        <v>3.589713955786022</v>
       </c>
       <c r="AX6" t="n">
-        <v>46.91659434986416</v>
+        <v>5.553679142024176</v>
       </c>
       <c r="AY6" t="n">
-        <v>266.8241790068947</v>
+        <v>44.36874759200608</v>
       </c>
       <c r="AZ6" t="n">
-        <v>25.80961963325334</v>
+        <v>39.31091262769046</v>
       </c>
       <c r="BA6" t="n">
         <v>-1.619</v>
@@ -1621,49 +1621,49 @@
         <v>24</v>
       </c>
       <c r="B7" t="n">
-        <v>15.52237759198443</v>
+        <v>21.91144252027471</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2972669327137361</v>
+        <v>0.2473854558685842</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00827044741359213</v>
+        <v>0.4027367983789142</v>
       </c>
       <c r="E7" t="n">
-        <v>8.722733926627253</v>
+        <v>4.648501467986514</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001242573337617079</v>
+        <v>0.001975923202674776</v>
       </c>
       <c r="G7" t="n">
-        <v>1.905434264712514</v>
+        <v>6.757427104864808</v>
       </c>
       <c r="H7" t="n">
-        <v>4.32466997504502</v>
+        <v>1.175136288895581</v>
       </c>
       <c r="I7" t="n">
-        <v>3.183752721197497</v>
+        <v>1.492432262335557</v>
       </c>
       <c r="J7" t="n">
-        <v>3.18621396446507</v>
+        <v>2.34454723783376</v>
       </c>
       <c r="K7" t="n">
-        <v>2.237054176787484</v>
+        <v>4.001365119514759</v>
       </c>
       <c r="L7" t="n">
-        <v>2.639741305892563</v>
+        <v>3.06928494970976</v>
       </c>
       <c r="M7" t="n">
-        <v>1.193681419538303</v>
+        <v>4.189932568914494</v>
       </c>
       <c r="N7" t="n">
-        <v>1.723597544672132</v>
+        <v>3.74724640868575</v>
       </c>
       <c r="O7" t="n">
         <v>104.65</v>
       </c>
       <c r="P7" t="n">
-        <v>0.001</v>
+        <v>0.5</v>
       </c>
       <c r="Q7" t="n">
         <v>0.11</v>
@@ -1672,7 +1672,7 @@
         <v>0.35</v>
       </c>
       <c r="S7" t="n">
-        <v>7.354294285576749</v>
+        <v>7.000929827843491</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1681,37 +1681,37 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>81.32937145368405</v>
+        <v>9.633154141668411</v>
       </c>
       <c r="W7" t="n">
         <v>100000</v>
       </c>
       <c r="X7" t="n">
-        <v>1.547947750441182</v>
+        <v>1.347286986106414</v>
       </c>
       <c r="Y7" t="n">
-        <v>60.98032327898827</v>
+        <v>60.3228121312688</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.9881040607536045</v>
+        <v>0.8400988680373623</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.003625144850183372</v>
+        <v>0.001408318631702893</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.06135621432299354</v>
+        <v>6.146397728838646</v>
       </c>
       <c r="AC7" t="n">
         <v>0.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>56.49609365229158</v>
+        <v>32.73597048073637</v>
       </c>
       <c r="AE7" t="n">
         <v>0.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.004613560062095413</v>
+        <v>0.01107643295140488</v>
       </c>
       <c r="AG7" t="n">
         <v>48</v>
@@ -1729,25 +1729,25 @@
         <v>0.83</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.017310324645986</v>
+        <v>1.306214317664138</v>
       </c>
       <c r="AM7" t="n">
-        <v>6.562191222184445</v>
+        <v>1.634305166326961</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>2.78314483999369</v>
+        <v>4.082534858446548</v>
       </c>
       <c r="AP7" t="n">
-        <v>13.64976756712682</v>
+        <v>15.27268483782863</v>
       </c>
       <c r="AQ7" t="n">
         <v>15.31</v>
       </c>
       <c r="AR7" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="AS7" t="n">
         <v>0.11</v>
@@ -1756,22 +1756,22 @@
         <v>1.3</v>
       </c>
       <c r="AU7" t="n">
-        <v>16.56819726099274</v>
+        <v>2.713596415439079</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.414361399463934</v>
+        <v>8.583725199907198</v>
       </c>
       <c r="AW7" t="n">
-        <v>21.08528390173183</v>
+        <v>5.912062934737125</v>
       </c>
       <c r="AX7" t="n">
-        <v>33.87813692424081</v>
+        <v>110.4993588685162</v>
       </c>
       <c r="AY7" t="n">
-        <v>50.66509598618173</v>
+        <v>12.80128835198379</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.986518738909272</v>
+        <v>105.4468832626658</v>
       </c>
       <c r="BA7" t="n">
         <v>-1.619</v>
@@ -1821,49 +1821,49 @@
         <v>24</v>
       </c>
       <c r="B8" t="n">
-        <v>3.891390473722628</v>
+        <v>1.419959587515241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6716716360342583</v>
+        <v>0.1209328706304831</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1079905439051008</v>
+        <v>0.00309528829396049</v>
       </c>
       <c r="E8" t="n">
-        <v>9.769024731983848</v>
+        <v>3.827696161299071</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02045509118351847</v>
+        <v>0.04777933577776907</v>
       </c>
       <c r="G8" t="n">
-        <v>14.3556729778797</v>
+        <v>32.06571854372453</v>
       </c>
       <c r="H8" t="n">
-        <v>2.922836652879346</v>
+        <v>3.96536464501889</v>
       </c>
       <c r="I8" t="n">
-        <v>2.296298607483519</v>
+        <v>2.737615038044541</v>
       </c>
       <c r="J8" t="n">
-        <v>1.205849378822387</v>
+        <v>1.696227991777619</v>
       </c>
       <c r="K8" t="n">
-        <v>9.174344157714399</v>
+        <v>9.910910653521235</v>
       </c>
       <c r="L8" t="n">
-        <v>8.454425024479606</v>
+        <v>8.781191314174846</v>
       </c>
       <c r="M8" t="n">
-        <v>1.066227687240824</v>
+        <v>2.279310053897376</v>
       </c>
       <c r="N8" t="n">
-        <v>3.561385075243187</v>
+        <v>1.616400974914579</v>
       </c>
       <c r="O8" t="n">
         <v>104.65</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5</v>
+        <v>0.001</v>
       </c>
       <c r="Q8" t="n">
         <v>0.11</v>
@@ -1872,7 +1872,7 @@
         <v>0.35</v>
       </c>
       <c r="S8" t="n">
-        <v>3.36333066081823</v>
+        <v>6.026242183287144</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1881,37 +1881,37 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>34.55494811029459</v>
+        <v>3.140721635082532</v>
       </c>
       <c r="W8" t="n">
         <v>100000</v>
       </c>
       <c r="X8" t="n">
-        <v>2.099218757024895</v>
+        <v>6.241662404668361</v>
       </c>
       <c r="Y8" t="n">
-        <v>46.91991146947734</v>
+        <v>53.62280674258832</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002003724429469213</v>
+        <v>0.3618871288541493</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.6227269486729339</v>
+        <v>0.2088914645713168</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.602009050054896</v>
+        <v>1.309366555385302</v>
       </c>
       <c r="AC8" t="n">
         <v>0.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>15.88464318862351</v>
+        <v>14.75936336485188</v>
       </c>
       <c r="AE8" t="n">
         <v>0.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.006799625456914293</v>
+        <v>0.04207376893125876</v>
       </c>
       <c r="AG8" t="n">
         <v>48</v>
@@ -1929,25 +1929,25 @@
         <v>0.83</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.69686282852086</v>
+        <v>7.329029856245281</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.111074983401099</v>
+        <v>1.492584497454328</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.925640031852098</v>
+        <v>1.63647590454164</v>
       </c>
       <c r="AP8" t="n">
-        <v>17.2737717698118</v>
+        <v>20.14487755129331</v>
       </c>
       <c r="AQ8" t="n">
         <v>15.31</v>
       </c>
       <c r="AR8" t="n">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="AS8" t="n">
         <v>0.11</v>
@@ -1956,22 +1956,22 @@
         <v>1.3</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.966193983677215</v>
+        <v>1.251003625025734</v>
       </c>
       <c r="AV8" t="n">
-        <v>13.29920564540239</v>
+        <v>4.745299603278153</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.075079537681249</v>
+        <v>2.292306983974447</v>
       </c>
       <c r="AX8" t="n">
-        <v>7.494505284708182</v>
+        <v>5.685716570297865</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.785103611199904</v>
+        <v>242.7473522546518</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7.870767992679159</v>
+        <v>123.9106566418059</v>
       </c>
       <c r="BA8" t="n">
         <v>-1.619</v>
@@ -2021,49 +2021,49 @@
         <v>24</v>
       </c>
       <c r="B9" t="n">
-        <v>1.163380875592019</v>
+        <v>8.43821933157539</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4141073380012303</v>
+        <v>0.3198913528418302</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2593339355114364</v>
+        <v>0.2320972569676558</v>
       </c>
       <c r="E9" t="n">
-        <v>3.860252830272614</v>
+        <v>2.556577823162587</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003146653466208297</v>
+        <v>0.05509913777881147</v>
       </c>
       <c r="G9" t="n">
-        <v>24.95859443069013</v>
+        <v>20.52624238634514</v>
       </c>
       <c r="H9" t="n">
-        <v>8.219739394194752</v>
+        <v>1.707878585136472</v>
       </c>
       <c r="I9" t="n">
-        <v>5.056312681697569</v>
+        <v>4.479399926702649</v>
       </c>
       <c r="J9" t="n">
-        <v>6.050992622435839</v>
+        <v>5.353377009001668</v>
       </c>
       <c r="K9" t="n">
-        <v>1.727709495838081</v>
+        <v>8.923997685867972</v>
       </c>
       <c r="L9" t="n">
-        <v>8.73793282208139</v>
+        <v>1.376050079683681</v>
       </c>
       <c r="M9" t="n">
-        <v>6.239834418425214</v>
+        <v>2.261101804783985</v>
       </c>
       <c r="N9" t="n">
-        <v>1.427529504941323</v>
+        <v>8.698265845526047</v>
       </c>
       <c r="O9" t="n">
         <v>104.65</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5</v>
+        <v>0.001</v>
       </c>
       <c r="Q9" t="n">
         <v>0.11</v>
@@ -2072,7 +2072,7 @@
         <v>0.35</v>
       </c>
       <c r="S9" t="n">
-        <v>2.266908987874961</v>
+        <v>2.696045493753418</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -2081,37 +2081,37 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>92.05349986840952</v>
+        <v>5.409833367293964</v>
       </c>
       <c r="W9" t="n">
         <v>100000</v>
       </c>
       <c r="X9" t="n">
-        <v>1.817403411264175</v>
+        <v>39.65662915808081</v>
       </c>
       <c r="Y9" t="n">
-        <v>44.83578146439995</v>
+        <v>66.69008530525052</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03235250980867351</v>
+        <v>0.02610258139392473</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.04394052556724366</v>
+        <v>0.003319862228906413</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.529869036861911</v>
+        <v>0.4031716009179181</v>
       </c>
       <c r="AC9" t="n">
         <v>0.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>10.94937500981717</v>
+        <v>35.62873324282462</v>
       </c>
       <c r="AE9" t="n">
         <v>0.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.4231027250053204</v>
+        <v>0.0049924593956471</v>
       </c>
       <c r="AG9" t="n">
         <v>48</v>
@@ -2129,25 +2129,25 @@
         <v>0.83</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.530523266700627</v>
+        <v>1.668075719956687</v>
       </c>
       <c r="AM9" t="n">
-        <v>2.346846678586495</v>
+        <v>2.887813756693153</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.780991301853134</v>
+        <v>1.313944833224326</v>
       </c>
       <c r="AP9" t="n">
-        <v>64.55316720527924</v>
+        <v>27.03533365401704</v>
       </c>
       <c r="AQ9" t="n">
         <v>15.31</v>
       </c>
       <c r="AR9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AS9" t="n">
         <v>0.11</v>
@@ -2156,22 +2156,22 @@
         <v>1.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>39.91145576246209</v>
+        <v>18.11389948036496</v>
       </c>
       <c r="AV9" t="n">
-        <v>13.3900038069803</v>
+        <v>1.056402091524215</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.714751389534066</v>
+        <v>27.10759617917142</v>
       </c>
       <c r="AX9" t="n">
-        <v>22.83464619162016</v>
+        <v>2.146845617018075</v>
       </c>
       <c r="AY9" t="n">
-        <v>69.27978413956187</v>
+        <v>16.68992784504087</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.665493820634949</v>
+        <v>25.83536713500661</v>
       </c>
       <c r="BA9" t="n">
         <v>-1.619</v>
@@ -2221,43 +2221,43 @@
         <v>24</v>
       </c>
       <c r="B10" t="n">
-        <v>24.31119981011818</v>
+        <v>87.24607028230011</v>
       </c>
       <c r="C10" t="n">
-        <v>0.006731893234896454</v>
+        <v>0.360660622197475</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1830144079342389</v>
+        <v>0.297383231809733</v>
       </c>
       <c r="E10" t="n">
-        <v>19.3580463631489</v>
+        <v>1.446109223005004</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07468661015877416</v>
+        <v>0.3304290064075137</v>
       </c>
       <c r="G10" t="n">
-        <v>40.24026800617218</v>
+        <v>6.359603704778544</v>
       </c>
       <c r="H10" t="n">
-        <v>4.188948709632963</v>
+        <v>5.134695276955973</v>
       </c>
       <c r="I10" t="n">
-        <v>2.467770020991745</v>
+        <v>1.154015334685048</v>
       </c>
       <c r="J10" t="n">
-        <v>2.568523307301584</v>
+        <v>1.790615443207512</v>
       </c>
       <c r="K10" t="n">
-        <v>2.206321970785715</v>
+        <v>5.463392373535065</v>
       </c>
       <c r="L10" t="n">
-        <v>4.59338086443397</v>
+        <v>2.032219414388026</v>
       </c>
       <c r="M10" t="n">
-        <v>4.066584357227869</v>
+        <v>4.780175745032301</v>
       </c>
       <c r="N10" t="n">
-        <v>2.487332855731655</v>
+        <v>6.158481154706084</v>
       </c>
       <c r="O10" t="n">
         <v>104.65</v>
@@ -2272,7 +2272,7 @@
         <v>0.35</v>
       </c>
       <c r="S10" t="n">
-        <v>4.764761073110518</v>
+        <v>2.357896013800342</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -2281,37 +2281,37 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>10.47149656453435</v>
+        <v>15.01322499318057</v>
       </c>
       <c r="W10" t="n">
         <v>100000</v>
       </c>
       <c r="X10" t="n">
-        <v>5.323234114832539</v>
+        <v>52.54256280474211</v>
       </c>
       <c r="Y10" t="n">
-        <v>62.01364687243713</v>
+        <v>49.07003340408517</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.4381791017788009</v>
+        <v>0.1597567825420678</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01669598207757709</v>
+        <v>0.01050411307744583</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.793105812279869</v>
+        <v>0.00398219934032714</v>
       </c>
       <c r="AC10" t="n">
         <v>0.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>45.58623248092</v>
+        <v>29.07901843085938</v>
       </c>
       <c r="AE10" t="n">
         <v>0.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.00764295573575936</v>
+        <v>0.0335541721316174</v>
       </c>
       <c r="AG10" t="n">
         <v>48</v>
@@ -2329,25 +2329,25 @@
         <v>0.83</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.086305859442327</v>
+        <v>2.634214331219345</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.821176368429866</v>
+        <v>1.682722285310845</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.389892626672453</v>
+        <v>1.923596083077274</v>
       </c>
       <c r="AP10" t="n">
-        <v>61.66876989842974</v>
+        <v>58.86982646490781</v>
       </c>
       <c r="AQ10" t="n">
         <v>15.31</v>
       </c>
       <c r="AR10" t="n">
-        <v>7.5</v>
+        <v>1</v>
       </c>
       <c r="AS10" t="n">
         <v>0.11</v>
@@ -2356,22 +2356,22 @@
         <v>1.3</v>
       </c>
       <c r="AU10" t="n">
-        <v>75.37920174282334</v>
+        <v>3.123959709422103</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.382214011154605</v>
+        <v>3.724242616453596</v>
       </c>
       <c r="AW10" t="n">
-        <v>16.10656023809455</v>
+        <v>9.041550637290364</v>
       </c>
       <c r="AX10" t="n">
-        <v>12.06675773247844</v>
+        <v>30.99650310278651</v>
       </c>
       <c r="AY10" t="n">
-        <v>211.7111147922239</v>
+        <v>25.60474779756239</v>
       </c>
       <c r="AZ10" t="n">
-        <v>57.40698583073245</v>
+        <v>15.01255935224741</v>
       </c>
       <c r="BA10" t="n">
         <v>-1.619</v>
